--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -82,9 +82,7 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -607,7 +605,7 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATOLA PLUS SEDEN HASTA UNA TALLA XL BUENA ENLONGACION </t>
+          <t>BATOLA PLUS SEDEN HASTA UNA TALLA XL BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -739,7 +737,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATOLA TALLA UNICA SEDE HASTA UNA TALLA L </t>
+          <t>BATOLA TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -805,7 +803,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BATOLA (TALLA UNICA) SEDE HASTA UNA TALLA L </t>
+          <t>BATOLA (TALLA UNICA) SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -933,7 +931,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA COMPRENDE DOS PRENDAS </t>
+          <t>TALLA UNICA COMPRENDE DOS PRENDAS</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1127,7 +1125,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA PLUS SEDE HASTA UNA XL </t>
+          <t>TALLA PLUS SEDE HASTA UNA XL</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1193,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA PLUS SEDE HASTA UNA XL </t>
+          <t>TALLA PLUS SEDE HASTA UNA XL</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1259,7 +1257,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA SEDE HASTA UNA TALLA L </t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1317,7 +1315,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION </t>
+          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1379,7 +1377,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA EN TELA BENGALINA BUENA ENLONGACION </t>
+          <t>TALLA UNICA EN TELA BENGALINA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1441,7 +1439,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA TELA BENGALINA MUY BUENA ENLONGACION </t>
+          <t>TALLA UNICA TELA BENGALINA MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1503,7 +1501,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA TELA BENGALINA BUENA ENLONGACION </t>
+          <t>TALLA UNICA TELA BENGALINA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1565,7 +1563,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA TELA BENGALINA BUENA ENLONGACION </t>
+          <t>TALLA UNICA TELA BENGALINA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1627,7 +1625,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA TELA BENGALINA BUENA ENLONGACION </t>
+          <t>TALLA UNICA TELA BENGALINA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1689,7 +1687,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION </t>
+          <t>TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1751,7 +1749,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA TELA BURDA ITALIANA BUENA ENLONGACON </t>
+          <t>TALLA UNICA TELA BURDA ITALIANA BUENA ENLONGACON</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1813,7 +1811,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA EN TELA ALGODON ITALIANO BUENA ENLONGACION </t>
+          <t>TALLA UNICA EN TELA ALGODON ITALIANO BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -1875,7 +1873,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION </t>
+          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -1937,7 +1935,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION </t>
+          <t>TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2003,7 +2001,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EN TALLA UNICA TELA BENGALINA </t>
+          <t>EN TALLA UNICA TELA BENGALINA</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2065,7 +2063,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION </t>
+          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2127,7 +2125,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA ÚNICA </t>
+          <t>TALLA ÚNICA</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2193,7 +2191,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEDE HASTA UNA TALLA L </t>
+          <t>SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2581,7 +2579,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPRENDE 4 PIEZAS TALLA UNICA BUENA ENLONGACION </t>
+          <t>COMPRENDE 4 PIEZAS TALLA UNICA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -2647,7 +2645,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA </t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -2713,7 +2711,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA SEDE HASTA UNA TALLA L </t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -2903,7 +2901,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disponible en Curva de Tallas </t>
+          <t>Disponible en Curva de Tallas</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3151,7 +3149,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISPONIBLE EN CURVA DE TALLAS TALLAJE NORMAL </t>
+          <t>DISPONIBLE EN CURVA DE TALLAS TALLAJE NORMAL</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3217,7 +3215,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISPONIBLE EN CURVA COMPLETA BUENA ENLONGACION </t>
+          <t>DISPONIBLE EN CURVA COMPLETA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3283,7 +3281,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA SEDE HASTA UNA TALLA L </t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3345,7 +3343,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA ÚNICA COMPRENDE TRES PIEZAS </t>
+          <t>TALLA ÚNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3411,7 +3409,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comprede 3 Piezas Talla Única Sede hasta una talla L </t>
+          <t>Comprede 3 Piezas Talla Única Sede hasta una talla L</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3477,7 +3475,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA MUY BUENA ENLONGACION </t>
+          <t>TALLA UNICA MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -3543,7 +3541,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA COMPRENDE 3 PIEZAS </t>
+          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -3609,7 +3607,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA PLUS SEDE PARA UNA TALLA XL </t>
+          <t>TALLA PLUS SEDE PARA UNA TALLA XL</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -3807,7 +3805,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA </t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -3935,7 +3933,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTILO CORSET TALLAS S-M-L </t>
+          <t>ESTILO CORSET TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -4183,7 +4181,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON VARILLA EN TALLAS S-M-L </t>
+          <t>CON VARILLA EN TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4373,7 +4371,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA PLUS </t>
+          <t>TALLA PLUS</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -4435,7 +4433,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLAS M/L L/XL </t>
+          <t>TALLAS M/L L/XL</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -4501,7 +4499,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA ESTILO OVERSIZE </t>
+          <t>TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -4567,7 +4565,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHORT TIRA PLUS SEDEN HASTA UNA XL </t>
+          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -4695,7 +4693,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA SEDE HASTA UNA TALLA L </t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -4761,7 +4759,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA SEDE HASTA UNA TALLA L </t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -4823,7 +4821,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA COMPRENDE TRES PIEZAS </t>
+          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -4889,7 +4887,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA PLUS SEDE HASTA UNA XL MUY BUENA ENLONGACION </t>
+          <t>TALLA PLUS SEDE HASTA UNA XL MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -4951,7 +4949,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA </t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5017,7 +5015,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA ESTILO OVERSIZE </t>
+          <t>TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5083,7 +5081,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA COMPRENDE TRES PIEZAS </t>
+          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5149,7 +5147,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA PLUS COMPRENDE 3 PIEZAS SEDE HASTA UNA XL </t>
+          <t>TALLA PLUS COMPRENDE 3 PIEZAS SEDE HASTA UNA XL</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5215,7 +5213,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPRENDE 3 PIEZAS TALLA UNICA ESTILO OVERSIZE </t>
+          <t>COMPRENDE 3 PIEZAS TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -5281,7 +5279,7 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPRENDE TRES PIEZAS SEDE HASTA UNA TALLA L </t>
+          <t>COMPRENDE TRES PIEZAS SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -5347,7 +5345,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA </t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -5405,7 +5403,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARIEDAD DE TALLAS PARA TODA LA FAMILIA </t>
+          <t>VARIEDAD DE TALLAS PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -5459,7 +5457,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISPONIBLES PARA TODA LA FAMILIA </t>
+          <t>DISPONIBLES PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -5517,7 +5515,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISPONIBLES EN TALLAS PARA TODA LA FAMILIA </t>
+          <t>DISPONIBLES EN TALLAS PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -5583,7 +5581,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA </t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -5645,7 +5643,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLAS UNICA </t>
+          <t>TALLAS UNICA</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -5707,7 +5705,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLAS UNICAS SEDEN HASTA UNA TALLA L </t>
+          <t>TALLAS UNICAS SEDEN HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -5769,7 +5767,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA </t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -5831,7 +5829,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA </t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -5963,7 +5961,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TALLA UNICA SEDE HASTA UNA TALLA L </t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6119,7 +6117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6172,22 +6170,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Con imagen</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
           <t>Fecha de extracción</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-12 20:40</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-12 22:46</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$88</definedName>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-12 22:46</t>
+          <t>2026-10-13 06:25</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$88</definedName>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 06:25</t>
+          <t>2026-10-13 02:14</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 02:14</t>
+          <t>2026-10-13 03:45</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 03:45</t>
+          <t>2026-10-13 04:26</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 04:26</t>
+          <t>2026-10-13 04:46</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$88</definedName>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 04:46</t>
+          <t>2026-10-13 12:24</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$88</definedName>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 12:24</t>
+          <t>2026-10-13 08:42</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 08:42</t>
+          <t>2026-10-13 09:42</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>OSA, cenicienta, Pinguinos, DEISY LILA, STICH</t>
+          <t>cenicienta, Pinguinos, DEISY LILA, STICH, OSA MOÑO</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/59s3cxnyzjf_1789405071463.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e3j2zd3xf5o_1789405073203.webp</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
@@ -5360,13 +5360,13 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
+          <t>241d370d-0a03-4406-ad18-a9a3755f21cb</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA FAMILIAR NAVIDEÑA</t>
+          <t>PIJAMA NAVIDAD FAMILIAR</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -5398,33 +5398,33 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Grinch Enojado, Reno Navidad</t>
+          <t>GRINCH ENOJADO, GRICH ENOJADO, SANTA VERDE</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>VARIEDAD DE TALLAS PARA TODA LA FAMILIA</t>
+          <t>Disponible en tallas para toda la familia</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3a06c6c2txt_1789404769078.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uc9c3z0a2am_1791910010182.webp</t>
         </is>
       </c>
       <c r="P77" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ffc59a3f-0bbb-4c8e-8f5a-dc6478217e7e</t>
+          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>PIJAMAS FAMILIARES</t>
+          <t>PIJAMA NAVIDEÑA DE PAREJA</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5437,13 +5437,17 @@
       <c r="G78" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" s="3" t="n"/>
+      <c r="H78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -5452,33 +5456,29 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>FAMILIA SIMPSONS, FAMILIA STICH, FAMILIA AVENGERS, FAMILIA IROMAN, FAMILIA CAPITAN AMERICA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>DISPONIBLES PARA TODA LA FAMILIA</t>
-        </is>
-      </c>
+          <t>Grinch Enojado, RENO VERDE, RENO BUFANDA, SANTA CARICTURA, SANTA, RENO CUADROS</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/iorl7i3h4x_1785715610130.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nenu0jwquta_1789404771647.webp</t>
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>35feb43b-d4ee-4cd0-97a4-a6461daee102</t>
+          <t>ffc59a3f-0bbb-4c8e-8f5a-dc6478217e7e</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA FAMILIAR NAVIDEÑAS</t>
+          <t>PIJAMAS FAMILIARES</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5491,12 +5491,8 @@
       <c r="G79" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H79" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n">
         <v>0</v>
       </c>
@@ -5510,64 +5506,56 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Grinch Enojado, Reno Nuevo, Santa y Mickey, Papá Noel reno, Santa Nieve</t>
+          <t>FAMILIA SIMPSONS, FAMILIA STICH, FAMILIA AVENGERS, FAMILIA IROMAN, FAMILIA CAPITAN AMERICA</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLES EN TALLAS PARA TODA LA FAMILIA</t>
+          <t>DISPONIBLES PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uo66j97t3qc_1789404070898.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/iorl7i3h4x_1785715610130.webp</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>237051ec-4251-4654-9e91-8b031dd0ac56</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>HOM-002</t>
-        </is>
-      </c>
+          <t>35feb43b-d4ee-4cd0-97a4-a6461daee102</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISERA PAREJA</t>
+          <t>PIJAMA FAMILIAR NAVIDEÑAS</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>pijama-pareja</t>
+          <t>familiar</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="3" t="n">
-        <v>95000</v>
+        <v>3</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>75000</v>
+        <v>2</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>73000</v>
+        <v>1</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -5576,33 +5564,37 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>BATMAN, STAR WARS</t>
+          <t>Grinch Enojado, Reno Nuevo, Santa y Mickey, Papá Noel reno, Santa Nieve, STICH, MICKEY, STICH ROJO, GRINCH ARBOLITO, STICH AZUL, MICKEY ROJO, MICKEY ARBOLITO, STICH BLANCO</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA</t>
+          <t>DISPONIBLES EN TALLAS PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/kyjp725ch0b_1784991424843.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uo66j97t3qc_1789404070898.webp</t>
         </is>
       </c>
       <c r="P80" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>7dcbe20c-5963-40c3-8164-3fe454daac65</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr"/>
+          <t>237051ec-4251-4654-9e91-8b031dd0ac56</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>HOM-002</t>
+        </is>
+      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PANTALON PAREJA (Copia)</t>
+          <t>PANTALON CAMISERA PAREJA</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5617,13 +5609,13 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>77000</v>
+        <v>95000</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>57000</v>
+        <v>75000</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>55000</v>
+        <v>73000</v>
       </c>
       <c r="J81" s="3" t="n">
         <v>0</v>
@@ -5638,33 +5630,33 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>BUGEES, VEGETA Y BULMA, PICAPIEDRAS, OSO BALENCIAGA, SIMPSOM DONA, AVENGERS, IRONAM, STICH, CAPITAN AMERICA, CAPIBARA, TOM Y JERRY, SUPERMAN</t>
+          <t>BATMAN, STAR WARS</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>TALLAS UNICA</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qxxc3xmungo_1787192967336.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/kyjp725ch0b_1784991424843.jpg</t>
         </is>
       </c>
       <c r="P81" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>89c96356-7731-47ac-bb8d-a4c4806c97c9</t>
+          <t>7dcbe20c-5963-40c3-8164-3fe454daac65</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PAREJA CORTA</t>
+          <t>PIJAMA PANTALON PAREJA (Copia)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5679,13 +5671,13 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>66000</v>
+        <v>77000</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>46000</v>
+        <v>57000</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>44000</v>
+        <v>55000</v>
       </c>
       <c r="J82" s="3" t="n">
         <v>0</v>
@@ -5700,38 +5692,38 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>SCOBBY DOOD, DONALD y DEISY, BATMAN, OSO BALENCIAGA</t>
+          <t>BUGEES, VEGETA Y BULMA, PICAPIEDRAS, OSO BALENCIAGA, SIMPSOM DONA, AVENGERS, IRONAM, STICH, CAPITAN AMERICA, CAPIBARA, TOM Y JERRY, SUPERMAN</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>TALLAS UNICAS SEDEN HASTA UNA TALLA L</t>
+          <t>TALLAS UNICA</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/k8f75qd94x_1791060978764.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qxxc3xmungo_1787192967336.webp</t>
         </is>
       </c>
       <c r="P82" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>1badab66-f476-403e-b23d-0eee029edbb5</t>
+          <t>89c96356-7731-47ac-bb8d-a4c4806c97c9</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>JUANITA BOLERO SUBLIMADA</t>
+          <t>PIJAMA PAREJA CORTA</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>shortiras</t>
+          <t>pijama-pareja</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -5741,13 +5733,13 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>20000</v>
+        <v>46000</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>190000</v>
+        <v>44000</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0</v>
@@ -5762,17 +5754,17 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>AVOCADO FUCSIA, GARFIELD, DEISY, OSO PANDA</t>
+          <t>SCOBBY DOOD, DONALD y DEISY, BATMAN, OSO BALENCIAGA</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLAS UNICAS SEDEN HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/so5z20eowjo_1791398900377.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/k8f75qd94x_1791060978764.webp</t>
         </is>
       </c>
       <c r="P83" s="2" t="n">
@@ -5782,13 +5774,13 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>f5e1c702-f8aa-4aa1-a440-26853e562d01</t>
+          <t>1badab66-f476-403e-b23d-0eee029edbb5</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>JUANITA BOLERO UNICOLOR</t>
+          <t>JUANITA BOLERO SUBLIMADA</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5803,13 +5795,13 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>16000</v>
+        <v>190000</v>
       </c>
       <c r="J84" s="3" t="n">
         <v>0</v>
@@ -5824,7 +5816,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
+          <t>AVOCADO FUCSIA, GARFIELD, DEISY, OSO PANDA</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -5834,27 +5826,23 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/so5z20eowjo_1791398900377.webp</t>
         </is>
       </c>
       <c r="P84" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SHD-001</t>
-        </is>
-      </c>
+          <t>f5e1c702-f8aa-4aa1-a440-26853e562d01</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA MUNDIALISTA</t>
+          <t>JUANITA BOLERO UNICOLOR</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5865,23 +5853,23 @@
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>25000</v>
+        <v>27000</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
@@ -5890,37 +5878,37 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
         </is>
       </c>
       <c r="P85" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
+          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>STU-001</t>
+          <t>SHD-001</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA</t>
+          <t>SHORT TIRA MUNDIALISTA</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5931,7 +5919,7 @@
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Única, Plus, Oversize</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
@@ -5947,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -5956,64 +5944,64 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, KITTY OSITO, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, CORAZONES CUADRO, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, COFFEE, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
+          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
         </is>
       </c>
       <c r="P86" s="2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>76053564-24d2-4662-9825-a044ec66f57a</t>
+          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SHD-004</t>
+          <t>STU-001</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA PLUS</t>
+          <t>SHORT TIRA</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>shorts</t>
+          <t>shortiras</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>33000</v>
+        <v>25000</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>23000</v>
+        <v>15000</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="J87" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
@@ -6022,37 +6010,37 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>OSO DORMILON, KOALA, JIRAFFA, PANTERA ROSA</t>
+          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, KITTY OSITO, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, CORAZONES CUADRO, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, COFFEE, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA PLUS SEDEN HASTA UNA TALLA XL</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxh01qefg3v_1784913347039.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
         </is>
       </c>
       <c r="P87" s="2" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>3bcb126b-7745-401c-b93d-acfd68a0fe7e</t>
+          <t>76053564-24d2-4662-9825-a044ec66f57a</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SCD1250</t>
+          <t>SHD-004</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA</t>
+          <t>SHORT CAMISA PLUS</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -6063,17 +6051,17 @@
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>27000</v>
+        <v>33000</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>0</v>
@@ -6088,25 +6076,91 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
+          <t>OSO DORMILON, KOALA, JIRAFFA, PANTERA ROSA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>SHORT CAMISA PLUS SEDEN HASTA UNA TALLA XL</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxh01qefg3v_1784913347039.jpg</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>3bcb126b-7745-401c-b93d-acfd68a0fe7e</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SCD1250</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>SHORT CAMISA</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>shorts</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>17000</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
           <t>OSO LILA, POLLITO, VAQUITA, GATICO FLOR, HELLO KITTY, CERDITO</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>TALLA UNICA SEDE HASTA UNA TALLA L.</t>
         </is>
       </c>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ujg84y11p3n_1784924351434.jpg</t>
         </is>
       </c>
-      <c r="P88" s="2" t="n">
+      <c r="P89" s="2" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P88"/>
+  <autoFilter ref="A1:P89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6152,7 +6206,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -6175,7 +6229,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 09:42</t>
+          <t>2026-10-13 13:17</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$89</definedName>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 13:17</t>
+          <t>2026-10-13 18:24</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$89</definedName>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 18:24</t>
+          <t>2026-10-13 14:49</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6229,7 +6229,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:49</t>
+          <t>2026-10-13 15:46</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2206,17 +2206,13 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>4e3f5d95-8f05-4444-8008-9e5e08a40abe</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>ET-001</t>
-        </is>
-      </c>
+          <t>9e4cc6dd-dee0-4bc8-971e-0917852ea52b</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO TIRA</t>
+          <t>ENTERIZO TIRAS NAVIDAD</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2225,11 +2221,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="3" t="n">
         <v>30000</v>
       </c>
@@ -2252,33 +2244,37 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>CERDITO</t>
+          <t>ARBOLITO, Cuadros rojos</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO TIRA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bw3xibgvppr_1784915289894.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/o06mdt8nwsg_1791926907779.webp</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>79f89726-a52c-4a0a-aef5-b348618f5651</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
+          <t>4e3f5d95-8f05-4444-8008-9e5e08a40abe</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ET-001</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO TIRAS</t>
+          <t>ENTERIZO TIRA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2293,13 +2289,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0</v>
@@ -2309,47 +2305,43 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>AMARILLO, SALMON, ROSA, ROSADO, AZUL, LILA</t>
+          <t>CERDITO</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>ENTERIZO TIRA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/f4gcx5fckbl_1785211250771.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bw3xibgvppr_1784915289894.jpg</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>e9c79d8f-5946-4f21-9571-917d1b04b061</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>PCH-003</t>
-        </is>
-      </c>
+          <t>79f89726-a52c-4a0a-aef5-b348618f5651</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISA HOMBRE</t>
+          <t>ENTERIZO TIRAS</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Enterizos</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2359,19 +2351,19 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>41000</v>
+        <v>27000</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>31000</v>
+        <v>17000</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>30000</v>
+        <v>16000</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -2380,37 +2372,37 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>VEGUETA, PICAPIEDRAS, PADRINO MAGICO, MESSY, MARVEL</t>
+          <t>AMARILLO, SALMON, ROSA, ROSADO, AZUL, LILA</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA (36)</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/mn99r1y1ls_1784949944792.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/f4gcx5fckbl_1785211250771.jpg</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>d408c8d9-4257-4a40-a884-f684922ced46</t>
+          <t>e9c79d8f-5946-4f21-9571-917d1b04b061</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>HOM-001</t>
+          <t>PCH-003</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>BERMUDA HOMBRE</t>
+          <t>PANTALON CAMISA HOMBRE</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2425,19 +2417,19 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>38000</v>
+        <v>41000</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>28000</v>
+        <v>31000</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -2446,42 +2438,42 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>MICKEY, STICH</t>
+          <t>VEGUETA, PICAPIEDRAS, PADRINO MAGICO, MESSY, MARVEL</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA SEDE HASTA UNA TALLA (36)</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA (36)</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ya25i5av86q_1784947907589.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/mn99r1y1ls_1784949944792.jpg</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>f28d98f2-3462-4bbb-97b5-9851c64804bc</t>
+          <t>d408c8d9-4257-4a40-a884-f684922ced46</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PJU-005</t>
+          <t>HOM-001</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PANTALON JUANITA ULICOLOR</t>
+          <t>BERMUDA HOMBRE</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Juanita</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2491,13 +2483,13 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>32000</v>
+        <v>38000</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>22000</v>
+        <v>28000</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -2512,33 +2504,37 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO, FLOR, HELLO KITTY AZUL</t>
+          <t>MICKEY, STICH</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA ÚNICA SEDE HASTA UNA TALLA (36)</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fchut0egg2l_1784948160684.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ya25i5av86q_1784947907589.jpg</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>929e1473-1c71-4111-be78-4a7e3757a0b2</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
+          <t>f28d98f2-3462-4bbb-97b5-9851c64804bc</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PJU-005</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>JUANITA 4 PIEZAS</t>
+          <t>PANTALON JUANITA ULICOLOR</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2553,13 +2549,13 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>28000</v>
+        <v>32000</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>0</v>
@@ -2574,37 +2570,33 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA MORADA, AVOCADO FUCSIA, STICH MORADO, KOALA, OSO LOTSO, MINNIE, CERDITO FUCSIA, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
+          <t>HELLO KITTY, OSO, FLOR, HELLO KITTY AZUL</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>COMPRENDE 4 PIEZAS TALLA UNICA BUENA ENLONGACION</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqwsrxvr1ic_1789406839500.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fchut0egg2l_1784948160684.jpg</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>673b49dd-0e8e-4f2a-8e8c-c89494d68101</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>JS107</t>
-        </is>
-      </c>
+          <t>929e1473-1c71-4111-be78-4a7e3757a0b2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>JUANITA SEXY SUBLIMADA</t>
+          <t>JUANITA 4 PIEZAS</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2619,13 +2611,13 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>24000</v>
+        <v>28000</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
@@ -2640,37 +2632,33 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO, PIOLIN</t>
+          <t>VAQUITA MORADA, AVOCADO FUCSIA, STICH MORADO, KOALA, OSO LOTSO, MINNIE, CERDITO FUCSIA, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>COMPRENDE 4 PIEZAS TALLA UNICA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/45rr6yv31td_1784947244400.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqwsrxvr1ic_1789406839500.webp</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>baef88f3-ffb4-407b-9afd-8f49877f0276</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>JS-003</t>
-        </is>
-      </c>
+          <t>1fc2c3f6-be41-49b6-a97b-c33cb5933cef</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>JUANITA SEXY UNICOLOR</t>
+          <t>JUANITA SEXY NAVIDAD</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2685,19 +2673,19 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -2706,42 +2694,42 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA, OSO TIERNO, MICKEY, STICH, POCHACO, OSO FUCSIA, ESTRELLAS, WINIE POOD, PERRITO, CORAZON LILA, OSO CORAZON, KITTY</t>
+          <t>SANTA, SANTA CARICATURAS, SANTA TRINEO</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>Talla única</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ceffp1umsxh_1784950731524.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8ny5hos4d9g_1791927026228.webp</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>db1b4f39-d39f-4371-8b3b-70ec2153b54f</t>
+          <t>673b49dd-0e8e-4f2a-8e8c-c89494d68101</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>LEV-003</t>
+          <t>JS107</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>LEVANTADORA TRIO</t>
+          <t>JUANITA SEXY SUBLIMADA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Levantadoras</t>
+          <t>Juanita</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2751,13 +2739,13 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>44000</v>
+        <v>24000</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>34000</v>
+        <v>14000</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>33000</v>
+        <v>13000</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0</v>
@@ -2772,56 +2760,64 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA, OSO DORMILON, POCHACO, AVOCADO FUCSIA, GATA MARIE</t>
+          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO, PIOLIN</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>LEVANTADORA TRIO</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/di0tb0nyeql_1784907641551.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/45rr6yv31td_1784947244400.jpg</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>221b3d57-e2c2-4d8e-b20f-4a227e9675f3</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr"/>
+          <t>baef88f3-ffb4-407b-9afd-8f49877f0276</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>JS-003</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TRIO NIÑAS</t>
+          <t>JUANITA SEXY UNICOLOR</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Juanita</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
       <c r="G37" s="3" t="n">
-        <v>39000</v>
+        <v>22000</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>29000</v>
+        <v>12000</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>28000</v>
+        <v>12000</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -2830,58 +2826,58 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>CERDITO, STICH, CENICIENTA, AVOCADO</t>
+          <t>VAQUITA, OSO TIERNO, MICKEY, STICH, POCHACO, OSO FUCSIA, ESTRELLAS, WINIE POOD, PERRITO, CORAZON LILA, OSO CORAZON, KITTY</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/imzbzaxzsp_1785213284628.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ceffp1umsxh_1784950731524.jpg</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>8d3a4a02-fe5b-4b4b-bc38-0a105eab5cfb</t>
+          <t>db1b4f39-d39f-4371-8b3b-70ec2153b54f</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PCN</t>
+          <t>LEV-003</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISA NIÑA</t>
+          <t>LEVANTADORA TRIO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Levantadoras</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2/4, 6/8, 10/12, 14/16</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>32000</v>
+        <v>44000</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>22000</v>
+        <v>34000</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21000</v>
+        <v>33000</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>0</v>
@@ -2896,17 +2892,17 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>cenicienta, Pinguinos, DEISY LILA, STICH, OSA MOÑO</t>
+          <t>VAQUITA, OSO DORMILON, POCHACO, AVOCADO FUCSIA, GATA MARIE</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Disponible en Curva de Tallas</t>
+          <t>LEVANTADORA TRIO</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e3j2zd3xf5o_1789405073203.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/di0tb0nyeql_1784907641551.jpg</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
@@ -2916,17 +2912,13 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>022d6e48-1835-454f-92f8-937c00625ad5</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>BN104</t>
-        </is>
-      </c>
+          <t>221b3d57-e2c2-4d8e-b20f-4a227e9675f3</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA NIÑA</t>
+          <t>PANTALON TRIO NIÑAS</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2935,19 +2927,15 @@
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>2/4, 6/8, 10/12, 14/16</t>
-        </is>
-      </c>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="3" t="n">
-        <v>27000</v>
+        <v>39000</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17000</v>
+        <v>29000</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>16000</v>
+        <v>28000</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>0</v>
@@ -2962,7 +2950,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>BULMA, BOB ESPONJA, OSO, PAYASITO, PINGUINO, OVEJA, WINNE POOH, ARIEL, GATA HUELLAS, OSA, CONEJO ESTRELLAS</t>
+          <t>CERDITO, STICH, CENICIENTA, AVOCADO</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -2972,27 +2960,27 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qrm1cm85f6_1789405836874.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/imzbzaxzsp_1785213284628.jpg</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>b83bfa51-838e-4d72-8107-300660806c65</t>
+          <t>8d3a4a02-fe5b-4b4b-bc38-0a105eab5cfb</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>BN102</t>
+          <t>PCN</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>BATOLA NIÑA</t>
+          <t>PANTALON CAMISA NIÑA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3001,15 +2989,19 @@
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G40" s="3" t="n">
-        <v>25000</v>
+        <v>32000</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>14000</v>
+        <v>21000</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -3022,48 +3014,60 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>cenicienta, Pinguinos, DEISY LILA, STICH, OSA MOÑO</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>TALLAS 2/4-6/8-10/12-14/16 TALLAJE NORMAL</t>
+          <t>Disponible en Curva de Tallas</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/b0oc4bgkm8b_1784915527640.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e3j2zd3xf5o_1789405073203.webp</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>616e6657-708b-474d-888b-b1752a032f5b</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr"/>
+          <t>022d6e48-1835-454f-92f8-937c00625ad5</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>BN104</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TRIO DE NIÑOS</t>
+          <t>SHORT CAMISA NIÑA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G41" s="3" t="n">
-        <v>39000</v>
+        <v>27000</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>28000</v>
+        <v>16000</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0</v>
@@ -3078,58 +3082,54 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>POKEMON, TOY STORY, CARS, DIONOSAURIO, CAPIBARA, GOKU, DEMON SKAYER, IROMAN, ONE PIECE, BATMAN</t>
+          <t>BULMA, BOB ESPONJA, OSO, PAYASITO, PINGUINO, OVEJA, WINNE POOH, ARIEL, GATA HUELLAS, OSA, CONEJO ESTRELLAS</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>CLMPRENDE TRES PIEZAS DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
+          <t>DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/g983o9wjbmm_1785213690452.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qrm1cm85f6_1789405836874.webp</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2f708066-5d01-4a63-aa7f-a66ca37719f9</t>
+          <t>b83bfa51-838e-4d72-8107-300660806c65</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PN101</t>
+          <t>BN102</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISA NIÑO</t>
+          <t>BATOLA NIÑA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>2/4, 6/8, 10/12, 14/16</t>
-        </is>
-      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="3" t="n">
-        <v>32000</v>
+        <v>25000</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>0</v>
@@ -3142,39 +3142,31 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>CAPITAN AMERICA, IROMAN, AVENGERS, BARTS, STICH, CAPITAN AMERICA BLANCO, BATMAN, BARTS SIMSOMP, NARUTO</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLE EN CURVA DE TALLAS TALLAJE NORMAL</t>
+          <t>TALLAS 2/4-6/8-10/12-14/16 TALLAJE NORMAL</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/m8a6el1a9h_1785205682420.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/b0oc4bgkm8b_1784915527640.jpg</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>49a86fb8-53e6-4339-9ffd-4aa3ce6873a5</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>BCN</t>
-        </is>
-      </c>
+          <t>616e6657-708b-474d-888b-b1752a032f5b</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>BERMUDA CAMISA NIÑO</t>
+          <t>PANTALON TRIO DE NIÑOS</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3183,20 +3175,16 @@
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>2/4, 6/8, 10/12, 14/16</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="3" t="n">
+        <v>39000</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>29000</v>
+      </c>
+      <c r="I43" s="3" t="n">
         <v>28000</v>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>17000</v>
-      </c>
       <c r="J43" s="3" t="n">
         <v>0</v>
       </c>
@@ -3210,58 +3198,58 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>STICH, SIMPSON, MICKEY, BOB ESPONJA, GOKU, IROMAN, DINO, SPAIDERMAN, MICKEY NEGRO, PICAPIEDRAS, SONNY</t>
+          <t>POKEMON, TOY STORY, CARS, DIONOSAURIO, CAPIBARA, GOKU, DEMON SKAYER, IROMAN, ONE PIECE, BATMAN</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLE EN CURVA COMPLETA BUENA ENLONGACION</t>
+          <t>CLMPRENDE TRES PIEZAS DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l7lomlcb9s_1789405548938.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/g983o9wjbmm_1785213690452.jpg</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>4d530fc3-f6e4-4f32-a352-7a41bf6e548a</t>
+          <t>2f708066-5d01-4a63-aa7f-a66ca37719f9</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PAD-004</t>
+          <t>PN101</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISERA DAMA</t>
+          <t>PANTALON CAMISA NIÑO</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Pantalones Dama</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>2/4, 6/8, 10/12, 14/16</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0</v>
@@ -3276,54 +3264,58 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>OVEJA NUBE, STAR WARS, SIMSOMPS</t>
+          <t>CAPITAN AMERICA, IROMAN, AVENGERS, BARTS, STICH, CAPITAN AMERICA BLANCO, BATMAN, BARTS SIMSOMP, NARUTO</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>DISPONIBLE EN CURVA DE TALLAS TALLAJE NORMAL</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/soebsoaf9a_1784923641827.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/m8a6el1a9h_1785205682420.jpg</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>b76e12a6-9971-4f97-99a1-914753584349</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr"/>
+          <t>49a86fb8-53e6-4339-9ffd-4aa3ce6873a5</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>BCN</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>PANTALON COQUETA TANGA</t>
+          <t>BERMUDA CAMISA NIÑO</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Pantalones Dama</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>2/4, 6/8, 10/12, 14/16</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>39000</v>
+        <v>28000</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29000</v>
+        <v>18000</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>28000</v>
+        <v>17000</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>0</v>
@@ -3338,37 +3330,37 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>PIOLIN, GATO ROSA, MY MELODDY, OSA CORAZONES, AVOCADO</t>
+          <t>STICH, SIMPSON, MICKEY, BOB ESPONJA, GOKU, IROMAN, DINO, SPAIDERMAN, MICKEY NEGRO, PICAPIEDRAS, SONNY</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA COMPRENDE TRES PIEZAS</t>
+          <t>DISPONIBLE EN CURVA COMPLETA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/76efmc2g288_1791399661792.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l7lomlcb9s_1789405548938.webp</t>
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>a33b8c41-afe2-4d95-b3cf-e3d852124a09</t>
+          <t>4d530fc3-f6e4-4f32-a352-7a41bf6e548a</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PBT</t>
+          <t>PAD-004</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>PANTALON BOLERO TANGA.</t>
+          <t>SHORT CAMISERA DAMA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3383,14 +3375,14 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>39000</v>
+        <v>40000</v>
       </c>
       <c r="H46" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>29000</v>
       </c>
-      <c r="I46" s="3" t="n">
-        <v>28000</v>
-      </c>
       <c r="J46" s="3" t="n">
         <v>0</v>
       </c>
@@ -3404,37 +3396,33 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>LOTTSO, 101 DALMATA, BURBUJA, CINAMORROL, MINNIE, KITTY, STICH MORADO, 1003733655, MICKEY, POCHACO, CAPIBARA</t>
+          <t>OVEJA NUBE, STAR WARS, SIMSOMPS</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Comprede 3 Piezas Talla Única Sede hasta una talla L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lztijdyhzrr_1787193266433.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/soebsoaf9a_1784923641827.jpg</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>9db66764-f682-4f29-9f2a-74120a6bfbda</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>PMLD</t>
-        </is>
-      </c>
+          <t>b76e12a6-9971-4f97-99a1-914753584349</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>PANTALON MANGA LARGA DAMA</t>
+          <t>PANTALON COQUETA TANGA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3470,37 +3458,37 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>GATA MARIE, GARFIEL, CINAMORROL, OSO LILA, MINNIE ROJA, PIOLIN</t>
+          <t>PIOLIN, GATO ROSA, MY MELODDY, OSA CORAZONES, AVOCADO</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA MUY BUENA ENLONGACION</t>
+          <t>TALLA ÚNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/z62o4q4ky7d_1786225187133.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/76efmc2g288_1791399661792.webp</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>888e5349-d67e-4fde-896a-d73c72e01c44</t>
+          <t>a33b8c41-afe2-4d95-b3cf-e3d852124a09</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>PET-</t>
+          <t>PBT</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TOP ESQUELETO</t>
+          <t>PANTALON BOLERO TANGA.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3536,37 +3524,37 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>CERDITO</t>
+          <t>LOTTSO, 101 DALMATA, BURBUJA, CINAMORROL, MINNIE, KITTY, STICH MORADO, 1003733655, MICKEY, POCHACO, CAPIBARA</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
+          <t>Comprede 3 Piezas Talla Única Sede hasta una talla L</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8n2pel9plzr_1785210700469.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lztijdyhzrr_1787193266433.webp</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>5192e31f-5f3e-420f-86fa-171d093d3d12</t>
+          <t>9db66764-f682-4f29-9f2a-74120a6bfbda</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PTP-003</t>
+          <t>PMLD</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TIRA PLUS</t>
+          <t>PANTALON MANGA LARGA DAMA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3577,7 +3565,7 @@
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
@@ -3602,37 +3590,37 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>ANGELICA, MINNIE ROJA, OSSO, DONALD, ALADDINO, SNOOPY, VAQUITA MOO, PINGUINOS, PLUTTO, KOALA, PANTERA ROSA, GARFIEL, STICH, TIGERS, BOB ESPONJA</t>
+          <t>GATA MARIE, GARFIEL, CINAMORROL, OSO LILA, MINNIE ROJA, PIOLIN</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS SEDE PARA UNA TALLA XL</t>
+          <t>TALLA UNICA MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3z8ms0l7vdp_1784912750113.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/z62o4q4ky7d_1786225187133.webp</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1604c1b6-9de6-4f63-86ad-974f776ecef0</t>
+          <t>888e5349-d67e-4fde-896a-d73c72e01c44</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>PCD103</t>
+          <t>PET-</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISETA</t>
+          <t>PANTALON TOP ESQUELETO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3647,13 +3635,13 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>36000</v>
+        <v>39000</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="J50" s="3" t="n">
         <v>0</v>
@@ -3668,37 +3656,37 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>CARLITOS, CERDITO, CHIMUELO, PIOLIN, VAQUITA, KOALA, PLUTO, CAPIBARA FLOR, STICH FUEGO, OSO LOTTSO, BOB ESPONJA, MICKEY DORMILON, JIRAFFA</t>
+          <t>CERDITO</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lvax3vg7hag_1784914577547.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8n2pel9plzr_1785210700469.jpg</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>83ebf033-cb6e-4a1c-a85b-7835f122ea37</t>
+          <t>5192e31f-5f3e-420f-86fa-171d093d3d12</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PAD-001</t>
+          <t>PTP-003</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TIRAS</t>
+          <t>PANTALON TIRA PLUS</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3709,17 +3697,17 @@
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>34000</v>
+        <v>39000</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>24000</v>
+        <v>29000</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>23000</v>
+        <v>28000</v>
       </c>
       <c r="J51" s="3" t="n">
         <v>0</v>
@@ -3734,37 +3722,37 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, HELLO KITTY, PATO DONALD</t>
+          <t>ANGELICA, MINNIE ROJA, OSSO, DONALD, ALADDINO, SNOOPY, VAQUITA MOO, PINGUINOS, PLUTTO, KOALA, PANTERA ROSA, GARFIEL, STICH, TIGERS, BOB ESPONJA</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA PLUS SEDE PARA UNA TALLA XL</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lzr466vorq_1784912376517.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3z8ms0l7vdp_1784912750113.jpg</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05c6ee82-8ae3-4399-8b67-fade58b8d79d</t>
+          <t>1604c1b6-9de6-4f63-86ad-974f776ecef0</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PCDM-</t>
+          <t>PCD103</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CORTE MEDIO</t>
+          <t>PANTALON CAMISETA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3779,13 +3767,13 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>22000</v>
+        <v>25000</v>
       </c>
       <c r="J52" s="3" t="n">
         <v>0</v>
@@ -3800,42 +3788,42 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>STICH</t>
+          <t>CARLITOS, CERDITO, CHIMUELO, PIOLIN, VAQUITA, KOALA, PLUTO, CAPIBARA FLOR, STICH FUEGO, OSO LOTTSO, BOB ESPONJA, MICKEY DORMILON, JIRAFFA</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/69jr9dn9xjk_1785210970260.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lvax3vg7hag_1784914577547.jpg</t>
         </is>
       </c>
       <c r="P52" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>23ab5a86-3b70-45bc-914b-9af5b5a8e85e</t>
+          <t>83ebf033-cb6e-4a1c-a85b-7835f122ea37</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PNK-001</t>
+          <t>PAD-001</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PINK</t>
+          <t>PANTALON TIRAS</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Pantalones Dama</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3845,13 +3833,13 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>28000</v>
+        <v>34000</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>0</v>
@@ -3866,7 +3854,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE, HELLO KITTY</t>
+          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, HELLO KITTY, PATO DONALD</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -3876,44 +3864,48 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/v0krnzso3j_1784948725231.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lzr466vorq_1784912376517.jpg</t>
         </is>
       </c>
       <c r="P53" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>fb84d852-bf79-4573-9986-2533fee9e7e1</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr"/>
+          <t>05c6ee82-8ae3-4399-8b67-fade58b8d79d</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>PCDM-</t>
+        </is>
+      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>SET LUPITA</t>
+          <t>PANTALON CORTE MEDIO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
+          <t>Pantalones Dama</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>S, M, L</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>46000</v>
+        <v>33000</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>36000</v>
+        <v>23000</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="J54" s="3" t="n">
         <v>0</v>
@@ -3928,54 +3920,58 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, VINOTINTO, ROJO</t>
+          <t>STICH</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>ESTILO CORSET TALLAS S-M-L</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ep029rxa8a9_1785718833355.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/69jr9dn9xjk_1785210970260.jpg</t>
         </is>
       </c>
       <c r="P54" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>e78bc16f-eb3a-4579-a9c0-5ba22019056c</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr"/>
+          <t>23ab5a86-3b70-45bc-914b-9af5b5a8e85e</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>PNK-001</t>
+        </is>
+      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SET CRETA</t>
+          <t>PIJAMA PINK</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>S, M, L</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>46000</v>
+        <v>28000</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>35000</v>
+        <v>17000</v>
       </c>
       <c r="J55" s="3" t="n">
         <v>0</v>
@@ -3990,33 +3986,33 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, NEGRO, ROJO</t>
+          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE, HELLO KITTY</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>TALLAS S-M-L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/6bowpox83om_1785716981956.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/v0krnzso3j_1784948725231.jpg</t>
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2d1bb0dc-e10e-4125-8a8a-9b290bc8dea2</t>
+          <t>fb84d852-bf79-4573-9986-2533fee9e7e1</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SET AURORA</t>
+          <t>SET LUPITA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4052,33 +4048,33 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>ROJO, NEGRO, BLANCO, VINOTINTO</t>
+          <t>BLANCO, VINOTINTO, ROJO</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>TALLAS S-M-L</t>
+          <t>ESTILO CORSET TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cw351gdhp9w_1785716795373.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ep029rxa8a9_1785718833355.webp</t>
         </is>
       </c>
       <c r="P56" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>f6a756c1-e2a7-4de1-bf68-95fc2bcb6eab</t>
+          <t>e78bc16f-eb3a-4579-a9c0-5ba22019056c</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SET CARTAGENA</t>
+          <t>SET CRETA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4114,7 +4110,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>NEGRO, ROJO, LILA, BLANCO</t>
+          <t>BLANCO, NEGRO, ROJO</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4124,23 +4120,23 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fu0o9sy5kv9_1785716248806.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/6bowpox83om_1785716981956.webp</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>6e456677-4e39-4c60-9f88-4bac91698de5</t>
+          <t>2d1bb0dc-e10e-4125-8a8a-9b290bc8dea2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>SET LINA</t>
+          <t>SET AURORA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4155,14 +4151,14 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>45000</v>
+        <v>46000</v>
       </c>
       <c r="H58" s="3" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I58" s="3" t="n">
         <v>35000</v>
       </c>
-      <c r="I58" s="3" t="n">
-        <v>34000</v>
-      </c>
       <c r="J58" s="3" t="n">
         <v>0</v>
       </c>
@@ -4181,12 +4177,12 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>CON VARILLA EN TALLAS S-M-L</t>
+          <t>TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hd7g4iuoebj_1785718550142.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cw351gdhp9w_1785716795373.webp</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
@@ -4196,13 +4192,13 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>c5494a8f-584c-4533-b646-be158b96c3f9</t>
+          <t>f6a756c1-e2a7-4de1-bf68-95fc2bcb6eab</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SET TANGA TRANSPARENTE</t>
+          <t>SET CARTAGENA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4217,13 +4213,13 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>37000</v>
+        <v>46000</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>26000</v>
+        <v>35000</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>0</v>
@@ -4238,7 +4234,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, NEGRO, ROJO</t>
+          <t>NEGRO, ROJO, LILA, BLANCO</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4248,23 +4244,23 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hr2yhxmvdc_1785716489297.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fu0o9sy5kv9_1785716248806.webp</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>10aa3e72-f092-4927-9f1e-9bd87f1b00b4</t>
+          <t>6e456677-4e39-4c60-9f88-4bac91698de5</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>SET PARIS</t>
+          <t>SET LINA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4279,13 +4275,13 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>33000</v>
+        <v>45000</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>23000</v>
+        <v>35000</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>22000</v>
+        <v>34000</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>0</v>
@@ -4300,17 +4296,17 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>VINOTINTO, BLANCO, NEGRO, ROJO</t>
+          <t>ROJO, NEGRO, BLANCO, VINOTINTO</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>TALLAS S-M-L</t>
+          <t>CON VARILLA EN TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/0pluslhpj7m_1785717182849.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hd7g4iuoebj_1785718550142.webp</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
@@ -4320,44 +4316,40 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>c98f7973-6d9d-4604-a2a0-8b7e6b47c42d</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SCD</t>
-        </is>
-      </c>
+          <t>c5494a8f-584c-4533-b646-be158b96c3f9</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISERA PLUS</t>
+          <t>SET TANGA TRANSPARENTE</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Short Dama</t>
+          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>S, M, L</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>44000</v>
+        <v>37000</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>34000</v>
+        <v>27000</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
@@ -4366,54 +4358,54 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>OJOS, MINNIE, HELLO KITTY, OSO PANDA, STICH</t>
+          <t>BLANCO, NEGRO, ROJO</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS</t>
+          <t>TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l8f7zp228yi_1785250753887.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hr2yhxmvdc_1785716489297.webp</t>
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ee0c9e00-4ef6-49e8-bd0c-cc4658163c4a</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>PS-0532</t>
-        </is>
-      </c>
+          <t>10aa3e72-f092-4927-9f1e-9bd87f1b00b4</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA EN SATIN</t>
+          <t>SET PARIS</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Short Dama</t>
+          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>S, M, L</t>
+        </is>
+      </c>
       <c r="G62" s="3" t="n">
-        <v>34000</v>
+        <v>33000</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="J62" s="3" t="n">
         <v>0</v>
@@ -4428,37 +4420,37 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>VINOTINTO, BLANCO, NEGRO, ROJO</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>TALLAS M/L L/XL</t>
+          <t>TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/xd9j7q8l55_1785211668886.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/0pluslhpj7m_1785717182849.webp</t>
         </is>
       </c>
       <c r="P62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>167648e0-7d81-42c8-82a1-56eb76230f9c</t>
+          <t>c98f7973-6d9d-4604-a2a0-8b7e6b47c42d</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SCO-005</t>
+          <t>SCD</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA OVERSIZE</t>
+          <t>SHORT CAMISERA PLUS</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4469,23 +4461,23 @@
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Oversize</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>32000</v>
+        <v>44000</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>22000</v>
+        <v>34000</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>21000</v>
+        <v>33000</v>
       </c>
       <c r="J63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -4494,17 +4486,17 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>LABUBU, STICH, GATA MARIE, CERDITO, AVOCADO</t>
+          <t>OJOS, MINNIE, HELLO KITTY, OSO PANDA, STICH</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA ESTILO OVERSIZE</t>
+          <t>TALLA PLUS</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/zt0i4vuxg2q_1784924942802.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l8f7zp228yi_1785250753887.jpg</t>
         </is>
       </c>
       <c r="P63" s="2" t="n">
@@ -4514,17 +4506,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
+          <t>ee0c9e00-4ef6-49e8-bd0c-cc4658163c4a</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>STP-002</t>
+          <t>PS-0532</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS</t>
+          <t>PIJAMA EN SATIN</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4533,19 +4525,15 @@
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Plus</t>
-        </is>
-      </c>
+      <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="3" t="n">
-        <v>30000</v>
+        <v>34000</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4560,37 +4548,37 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1003145115, RULERGS, OSO ANTIFAZ, COFFE, PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
+          <t>TALLAS M/L L/XL</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/q027f72zlv8_1784914996896.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/xd9j7q8l55_1785211668886.jpg</t>
         </is>
       </c>
       <c r="P64" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
+          <t>167648e0-7d81-42c8-82a1-56eb76230f9c</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SET104</t>
+          <t>SCO-005</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>SHORT CAMISA OVERSIZE</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4601,17 +4589,17 @@
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Oversize</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>30000</v>
+        <v>32000</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="J65" s="3" t="n">
         <v>0</v>
@@ -4626,33 +4614,37 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
+          <t>LABUBU, STICH, GATA MARIE, CERDITO, AVOCADO</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/zt0i4vuxg2q_1784924942802.jpg</t>
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>db868027-05ab-43da-b546-090a8bfb7db5</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr"/>
+          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SET104</t>
+        </is>
+      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA DAMA</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4667,13 +4659,13 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="J66" s="3" t="n">
         <v>0</v>
@@ -4688,37 +4680,37 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>BOB ESPONJA, MICKEY, AVOCADO</t>
+          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/66paf71xy1x_1785211377717.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>7596d757-8fa0-4cfa-b1ea-05020cf6576d</t>
+          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SL-006</t>
+          <t>STP-002</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>SHORT LOLITA</t>
+          <t>SHORT TIRA PLUS</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4729,14 +4721,14 @@
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>19000</v>
@@ -4754,33 +4746,33 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>MICKEY, VAQUITA, AVOCADO, STICH</t>
+          <t>1003145115, RULERGS, OSO ANTIFAZ, COFFE, PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/03pl1niffof5_1784948410390.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/q027f72zlv8_1784914996896.jpg</t>
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>1c07b490-194e-4d0d-9b23-8db44a3074eb</t>
+          <t>db868027-05ab-43da-b546-090a8bfb7db5</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SHORT COQUETA</t>
+          <t>SHORT CAMISA DAMA</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4795,14 +4787,14 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="H68" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I68" s="3" t="n">
         <v>17000</v>
       </c>
-      <c r="I68" s="3" t="n">
-        <v>16000</v>
-      </c>
       <c r="J68" s="3" t="n">
         <v>0</v>
       </c>
@@ -4816,37 +4808,37 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>COME GALLETA, MICKEY, MINNIE, POCHACO</t>
+          <t>BOB ESPONJA, MICKEY, AVOCADO</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ttnjnuimxyk_1785213579780.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/66paf71xy1x_1785211377717.jpg</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>0d91b05e-0729-4465-b113-6a4d889a4bf7</t>
+          <t>7596d757-8fa0-4cfa-b1ea-05020cf6576d</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>JSP-008</t>
+          <t>SL-006</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SHORT JUANITA PLUS</t>
+          <t>SHORT LOLITA</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4857,17 +4849,17 @@
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="J69" s="3" t="n">
         <v>0</v>
@@ -4882,38 +4874,38 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>BURBUJA, MY MELODDI, DEISY, OSO, PIOLIN, JIRAFA</t>
+          <t>MICKEY, VAQUITA, AVOCADO, STICH</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS SEDE HASTA UNA XL MUY BUENA ENLONGACION</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqtwgozcis_1785000102336.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/03pl1niffof5_1784948410390.jpg</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12c5e812-44c1-40ac-baec-0f01c893b373</t>
+          <t>1c07b490-194e-4d0d-9b23-8db44a3074eb</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>CHAQUETA ANTIFLUIDO</t>
+          <t>SHORT COQUETA</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Sin categoría</t>
+          <t>Short Dama</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4923,13 +4915,13 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>40000</v>
+        <v>27000</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>29000</v>
+        <v>16000</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
@@ -4944,58 +4936,58 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>TOTTO, WINNE POOH, WINNE POOH LILA</t>
+          <t>COME GALLETA, MICKEY, MINNIE, POCHACO</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bbfyrwx0vfu_1785213166473.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ttnjnuimxyk_1785213579780.jpg</t>
         </is>
       </c>
       <c r="P70" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>a687b655-eda4-4a0d-83f4-5d6ea274e2aa</t>
+          <t>0d91b05e-0729-4465-b113-6a4d889a4bf7</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>SCO</t>
+          <t>JSP-008</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA OVERSIZE UNICOLOR</t>
+          <t>SHORT JUANITA PLUS</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Sin categoría</t>
+          <t>Short Dama</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
@@ -5010,58 +5002,54 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>BEIZ, ROJO, SALMÓN, AMARILLO, FUCSIA, NEGRO, AZUL, ROSADO</t>
+          <t>BURBUJA, MY MELODDI, DEISY, OSO, PIOLIN, JIRAFA</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA ESTILO OVERSIZE</t>
+          <t>TALLA PLUS SEDE HASTA UNA XL MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/38qfshu6kkf_1785211937680.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqtwgozcis_1785000102336.jpg</t>
         </is>
       </c>
       <c r="P71" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>050b8c7d-3cbf-42f4-954e-3c74521decc0</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
+          <t>12c5e812-44c1-40ac-baec-0f01c893b373</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA TRIO PAREJA</t>
+          <t>CHAQUETA ANTIFLUIDO</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Trios</t>
+          <t>Sin categoría</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>94000</v>
+        <v>40000</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>74000</v>
+        <v>30000</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>72000</v>
+        <v>29000</v>
       </c>
       <c r="J72" s="3" t="n">
         <v>0</v>
@@ -5076,58 +5064,58 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1003558423, 1003558424, 1003558425, 1003558426, 1003558427</t>
+          <t>TOTTO, WINNE POOH, WINNE POOH LILA</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/tjxjxutxyaj_1785205292625.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bbfyrwx0vfu_1785213166473.jpg</t>
         </is>
       </c>
       <c r="P72" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>636942f3-00d7-402f-95bb-ad8a4cfc82ce</t>
+          <t>a687b655-eda4-4a0d-83f4-5d6ea274e2aa</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PTP-002</t>
+          <t>SCO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TRIO PLUS</t>
+          <t>SHORT CAMISA OVERSIZE UNICOLOR</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Trios</t>
+          <t>Sin categoría</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>48000</v>
+        <v>30000</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>38000</v>
+        <v>20000</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>37000</v>
+        <v>19000</v>
       </c>
       <c r="J73" s="3" t="n">
         <v>0</v>
@@ -5142,37 +5130,37 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, DEISY, CAPIBARA, MINNIE, MAFALDA, OVEJA NUBE, AVOCADO, OSO BEARS, BETYU BOOP, SHICH, PANTERA ROSA</t>
+          <t>BEIZ, ROJO, SALMÓN, AMARILLO, FUCSIA, NEGRO, AZUL, ROSADO</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS COMPRENDE 3 PIEZAS SEDE HASTA UNA XL</t>
+          <t>TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3ccjn2e0yqn_1785010981212.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/38qfshu6kkf_1785211937680.jpg</t>
         </is>
       </c>
       <c r="P73" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>88515395-2f66-4a68-9d2b-2f598f2a9386</t>
+          <t>050b8c7d-3cbf-42f4-954e-3c74521decc0</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>TRI-005</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>TRIO OVERSIZE DAMA</t>
+          <t>PIJAMA TRIO PAREJA</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5187,13 +5175,13 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>44000</v>
+        <v>94000</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>34000</v>
+        <v>74000</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>33000</v>
+        <v>72000</v>
       </c>
       <c r="J74" s="3" t="n">
         <v>0</v>
@@ -5208,37 +5196,37 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
+          <t>1003558423, 1003558424, 1003558425, 1003558426, 1003558427</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>COMPRENDE 3 PIEZAS TALLA UNICA ESTILO OVERSIZE</t>
+          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e0wxiek6bya_1784951657522.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/tjxjxutxyaj_1785205292625.jpg</t>
         </is>
       </c>
       <c r="P74" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>c0e4735f-c320-4741-a9d0-d2c37f06b00e</t>
+          <t>636942f3-00d7-402f-95bb-ad8a4cfc82ce</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>TRI-004</t>
+          <t>PTP-002</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>PANTALON LOLITA</t>
+          <t>PANTALON TRIO PLUS</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5249,17 +5237,17 @@
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H75" s="3" t="n">
         <v>38000</v>
       </c>
-      <c r="H75" s="3" t="n">
-        <v>28000</v>
-      </c>
       <c r="I75" s="3" t="n">
-        <v>27000</v>
+        <v>37000</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0</v>
@@ -5274,58 +5262,58 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>MINNIE, DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
+          <t>HELLO KITTY, DEISY, CAPIBARA, MINNIE, MAFALDA, OVEJA NUBE, AVOCADO, OSO BEARS, BETYU BOOP, SHICH, PANTERA ROSA</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>COMPRENDE TRES PIEZAS SEDE HASTA UNA TALLA L</t>
+          <t>TALLA PLUS COMPRENDE 3 PIEZAS SEDE HASTA UNA XL</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/njirlp0s9_1784991741310.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3ccjn2e0yqn_1785010981212.jpg</t>
         </is>
       </c>
       <c r="P75" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>514e5dfc-3d76-4103-be01-5a67ca1668a5</t>
+          <t>88515395-2f66-4a68-9d2b-2f598f2a9386</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>VES-001</t>
+          <t>TRI-005</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VESTIDO MOSCHINO</t>
+          <t>TRIO OVERSIZE DAMA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Vestidos</t>
+          <t>Trios</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Oversize</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>36000</v>
+        <v>44000</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>26000</v>
+        <v>34000</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>25000</v>
+        <v>33000</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0</v>
@@ -5340,17 +5328,17 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>GALFIER, DONALD, BOB ESPONJA, STICH, ANGELICA, HELLO KITTY</t>
+          <t>OSO LOTSO, POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>COMPRENDE 3 PIEZAS TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxvkwf1vifk_1784950374041.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e0wxiek6bya_1784951657522.jpg</t>
         </is>
       </c>
       <c r="P76" s="2" t="n">
@@ -5360,30 +5348,38 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>241d370d-0a03-4406-ad18-a9a3755f21cb</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr"/>
+          <t>c0e4735f-c320-4741-a9d0-d2c37f06b00e</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>TRI-004</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA NAVIDAD FAMILIAR</t>
+          <t>PANTALON LOLITA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>familiar</t>
+          <t>Trios</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
       <c r="G77" s="3" t="n">
-        <v>3</v>
+        <v>38000</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>2</v>
+        <v>28000</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>1</v>
+        <v>27000</v>
       </c>
       <c r="J77" s="3" t="n">
         <v>0</v>
@@ -5398,56 +5394,64 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>GRINCH ENOJADO, GRICH ENOJADO, SANTA VERDE</t>
+          <t>MINNIE, DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Disponible en tallas para toda la familia</t>
+          <t>COMPRENDE TRES PIEZAS SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uc9c3z0a2am_1791910010182.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/njirlp0s9_1784991741310.jpg</t>
         </is>
       </c>
       <c r="P77" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr"/>
+          <t>514e5dfc-3d76-4103-be01-5a67ca1668a5</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>VES-001</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA NAVIDEÑA DE PAREJA</t>
+          <t>VESTIDO MOSCHINO</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>familiar</t>
+          <t>Vestidos</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
       <c r="G78" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1</v>
+        <v>25000</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -5456,29 +5460,33 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Grinch Enojado, RENO VERDE, RENO BUFANDA, SANTA CARICTURA, SANTA, RENO CUADROS</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>GALFIER, DONALD, BOB ESPONJA, STICH, ANGELICA, HELLO KITTY</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>TALLA UNICA</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nenu0jwquta_1789404771647.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxvkwf1vifk_1784950374041.jpg</t>
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ffc59a3f-0bbb-4c8e-8f5a-dc6478217e7e</t>
+          <t>241d370d-0a03-4406-ad18-a9a3755f21cb</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>PIJAMAS FAMILIARES</t>
+          <t>PIJAMA NAVIDAD FAMILIAR</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5491,13 +5499,17 @@
       <c r="G79" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
+      <c r="H79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -5506,33 +5518,33 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>FAMILIA SIMPSONS, FAMILIA STICH, FAMILIA AVENGERS, FAMILIA IROMAN, FAMILIA CAPITAN AMERICA</t>
+          <t>GRINCH ENOJADO, GRICH ENOJADO, SANTA VERDE</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLES PARA TODA LA FAMILIA</t>
+          <t>Disponible en tallas para toda la familia</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/iorl7i3h4x_1785715610130.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uc9c3z0a2am_1791910010182.webp</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>35feb43b-d4ee-4cd0-97a4-a6461daee102</t>
+          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA FAMILIAR NAVIDEÑAS</t>
+          <t>PIJAMA NAVIDEÑA DE PAREJA</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5555,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -5564,64 +5576,48 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Grinch Enojado, Reno Nuevo, Santa y Mickey, Papá Noel reno, Santa Nieve, STICH, MICKEY, STICH ROJO, GRINCH ARBOLITO, STICH AZUL, MICKEY ROJO, MICKEY ARBOLITO, STICH BLANCO</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>DISPONIBLES EN TALLAS PARA TODA LA FAMILIA</t>
-        </is>
-      </c>
+          <t>Grinch Enojado, RENO VERDE, RENO BUFANDA, SANTA CARICTURA, SANTA, RENO CUADROS</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uo66j97t3qc_1789404070898.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nenu0jwquta_1789404771647.webp</t>
         </is>
       </c>
       <c r="P80" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>237051ec-4251-4654-9e91-8b031dd0ac56</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>HOM-002</t>
-        </is>
-      </c>
+          <t>ffc59a3f-0bbb-4c8e-8f5a-dc6478217e7e</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISERA PAREJA</t>
+          <t>PIJAMAS FAMILIARES</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>pijama-pareja</t>
+          <t>familiar</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="3" t="n">
-        <v>95000</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>73000</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
       <c r="J81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
@@ -5630,60 +5626,56 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>BATMAN, STAR WARS</t>
+          <t>FAMILIA SIMPSONS, FAMILIA STICH, FAMILIA AVENGERS, FAMILIA IROMAN, FAMILIA CAPITAN AMERICA</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA</t>
+          <t>DISPONIBLES PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/kyjp725ch0b_1784991424843.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/iorl7i3h4x_1785715610130.webp</t>
         </is>
       </c>
       <c r="P81" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>7dcbe20c-5963-40c3-8164-3fe454daac65</t>
+          <t>35feb43b-d4ee-4cd0-97a4-a6461daee102</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PANTALON PAREJA (Copia)</t>
+          <t>PIJAMA FAMILIAR NAVIDEÑAS</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>pijama-pareja</t>
+          <t>familiar</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="3" t="n">
-        <v>77000</v>
+        <v>3</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>57000</v>
+        <v>2</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>55000</v>
+        <v>1</v>
       </c>
       <c r="J82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -5692,17 +5684,17 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>BUGEES, VEGETA Y BULMA, PICAPIEDRAS, OSO BALENCIAGA, SIMPSOM DONA, AVENGERS, IRONAM, STICH, CAPITAN AMERICA, CAPIBARA, TOM Y JERRY, SUPERMAN</t>
+          <t>Grinch Enojado, Reno Nuevo, Santa y Mickey, Papá Noel reno, Santa Nieve, STICH, MICKEY, STICH ROJO, GRINCH ARBOLITO, STICH AZUL, MICKEY ROJO, MICKEY ARBOLITO, STICH BLANCO</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>TALLAS UNICA</t>
+          <t>DISPONIBLES EN TALLAS PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qxxc3xmungo_1787192967336.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uo66j97t3qc_1789404070898.webp</t>
         </is>
       </c>
       <c r="P82" s="2" t="n">
@@ -5712,13 +5704,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>89c96356-7731-47ac-bb8d-a4c4806c97c9</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr"/>
+          <t>237051ec-4251-4654-9e91-8b031dd0ac56</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>HOM-002</t>
+        </is>
+      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PAREJA CORTA</t>
+          <t>PANTALON CAMISERA PAREJA</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5733,13 +5729,13 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>66000</v>
+        <v>95000</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>46000</v>
+        <v>75000</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>44000</v>
+        <v>73000</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0</v>
@@ -5754,38 +5750,38 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SCOBBY DOOD, DONALD y DEISY, BATMAN, OSO BALENCIAGA</t>
+          <t>BATMAN, STAR WARS</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>TALLAS UNICAS SEDEN HASTA UNA TALLA L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/k8f75qd94x_1791060978764.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/kyjp725ch0b_1784991424843.jpg</t>
         </is>
       </c>
       <c r="P83" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>1badab66-f476-403e-b23d-0eee029edbb5</t>
+          <t>7dcbe20c-5963-40c3-8164-3fe454daac65</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>JUANITA BOLERO SUBLIMADA</t>
+          <t>PIJAMA PANTALON PAREJA (Copia)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>shortiras</t>
+          <t>pijama-pareja</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -5795,13 +5791,13 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>30000</v>
+        <v>77000</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>20000</v>
+        <v>57000</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>190000</v>
+        <v>55000</v>
       </c>
       <c r="J84" s="3" t="n">
         <v>0</v>
@@ -5816,38 +5812,38 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>AVOCADO FUCSIA, GARFIELD, DEISY, OSO PANDA</t>
+          <t>BUGEES, VEGETA Y BULMA, PICAPIEDRAS, OSO BALENCIAGA, SIMPSOM DONA, AVENGERS, IRONAM, STICH, CAPITAN AMERICA, CAPIBARA, TOM Y JERRY, SUPERMAN</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLAS UNICA</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/so5z20eowjo_1791398900377.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qxxc3xmungo_1787192967336.webp</t>
         </is>
       </c>
       <c r="P84" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>f5e1c702-f8aa-4aa1-a440-26853e562d01</t>
+          <t>89c96356-7731-47ac-bb8d-a4c4806c97c9</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>JUANITA BOLERO UNICOLOR</t>
+          <t>PIJAMA PAREJA CORTA</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>shortiras</t>
+          <t>pijama-pareja</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -5857,13 +5853,13 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>27000</v>
+        <v>66000</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>17000</v>
+        <v>46000</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>16000</v>
+        <v>44000</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0</v>
@@ -5878,37 +5874,33 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
+          <t>SCOBBY DOOD, DONALD y DEISY, BATMAN, OSO BALENCIAGA</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLAS UNICAS SEDEN HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/k8f75qd94x_1791060978764.webp</t>
         </is>
       </c>
       <c r="P85" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>SHD-001</t>
-        </is>
-      </c>
+          <t>1badab66-f476-403e-b23d-0eee029edbb5</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA MUNDIALISTA</t>
+          <t>JUANITA BOLERO SUBLIMADA</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5919,23 +5911,23 @@
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>14000</v>
+        <v>190000</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -5944,37 +5936,33 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>AVOCADO FUCSIA, GARFIELD, DEISY, OSO PANDA</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/so5z20eowjo_1791398900377.webp</t>
         </is>
       </c>
       <c r="P86" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>STU-001</t>
-        </is>
-      </c>
+          <t>54e67993-b96c-4d86-93f3-bcfcda1a7d6c</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA</t>
+          <t>SHORT LOLITA NAVIDAD</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5989,13 +5977,13 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="J87" s="3" t="n">
         <v>0</v>
@@ -6010,64 +5998,60 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, KITTY OSITO, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, CORAZONES CUADRO, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, COFFEE, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
+          <t>CAMPANAS</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ogs30ui080p_1791926800097.webp</t>
         </is>
       </c>
       <c r="P87" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>76053564-24d2-4662-9825-a044ec66f57a</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>SHD-004</t>
-        </is>
-      </c>
+          <t>f5e1c702-f8aa-4aa1-a440-26853e562d01</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA PLUS</t>
+          <t>JUANITA BOLERO UNICOLOR</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>shorts</t>
+          <t>shortiras</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>33000</v>
+        <v>27000</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
@@ -6076,42 +6060,42 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>OSO DORMILON, KOALA, JIRAFFA, PANTERA ROSA</t>
+          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA PLUS SEDEN HASTA UNA TALLA XL</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxh01qefg3v_1784913347039.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
         </is>
       </c>
       <c r="P88" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>3bcb126b-7745-401c-b93d-acfd68a0fe7e</t>
+          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SCD1250</t>
+          <t>STU-001</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA</t>
+          <t>SHORT TIRA</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>shorts</t>
+          <t>shortiras</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -6121,46 +6105,364 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SHD-001</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>SHORT TIRA MUNDIALISTA</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>shortiras</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Única, Plus, Oversize</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>76053564-24d2-4662-9825-a044ec66f57a</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SHD-004</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>SHORT CAMISA PLUS</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>shorts</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Plus</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>22000</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>OSO DORMILON, KOALA, JIRAFFA, PANTERA ROSA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>SHORT CAMISA PLUS SEDEN HASTA UNA TALLA XL</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxh01qefg3v_1784913347039.jpg</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>1dfacdb0-1d31-4c49-9a3e-ae522295b8e1</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>TRIO PANDA NAVIDAD</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>shorts</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>SANAT TRINEO, SANTA CARICATURA, SANTA TRINEO</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/9yveawjb88_1791927248517.webp</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2cd0b6cd-a7bc-4009-ab40-34050bc02a02</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>SHORT COQUETA TANGA NAVIDAD</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>shorts</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="H89" s="3" t="n">
+      <c r="H93" s="3" t="n">
         <v>17000</v>
       </c>
-      <c r="I89" s="3" t="n">
+      <c r="I93" s="3" t="n">
         <v>16000</v>
       </c>
-      <c r="J89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="2" t="n">
+      <c r="J93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>MICKEY, GRINCH, STICH ROJO</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>TALLA UNICA</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vxa9pwoeth9_1791927134958.webp</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>3bcb126b-7745-401c-b93d-acfd68a0fe7e</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SCD1250</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>SHORT CAMISA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>shorts</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>17000</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>OSO LILA, POLLITO, VAQUITA, GATICO FLOR, HELLO KITTY, CERDITO</t>
         </is>
       </c>
-      <c r="N89" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>TALLA UNICA SEDE HASTA UNA TALLA L.</t>
         </is>
       </c>
-      <c r="O89" s="2" t="inlineStr">
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ujg84y11p3n_1784924351434.jpg</t>
         </is>
       </c>
-      <c r="P89" s="2" t="n">
+      <c r="P94" s="2" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P89"/>
+  <autoFilter ref="A1:P94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6206,7 +6508,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -6218,7 +6520,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -6229,7 +6531,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-13 15:46</t>
+          <t>2026-10-14 00:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6531,7 +6531,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:35</t>
+          <t>2026-10-14 06:33</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6531,7 +6531,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 06:33</t>
+          <t>2026-10-14 12:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -2927,7 +2927,11 @@
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G39" s="3" t="n">
         <v>39000</v>
       </c>
@@ -3175,7 +3179,11 @@
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G43" s="3" t="n">
         <v>39000</v>
       </c>
@@ -5495,7 +5503,11 @@
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Única, Plus, S, M, L, 2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G79" s="3" t="n">
         <v>3</v>
       </c>
@@ -6531,7 +6543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 12:35</t>
+          <t>2026-10-14 18:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 18:34</t>
+          <t>2026-10-15 00:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 00:34</t>
+          <t>2026-10-15 06:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 06:34</t>
+          <t>2026-10-15 12:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 12:35</t>
+          <t>2026-10-15 18:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -5488,13 +5488,13 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>241d370d-0a03-4406-ad18-a9a3755f21cb</t>
+          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA NAVIDAD FAMILIAR</t>
+          <t>PIJAMA NAVIDEÑA DE PAREJA</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5505,17 +5505,17 @@
       <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, S, M, L, 2/4, 6/8, 10/12, 14/16</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>3</v>
+        <v>59000</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2</v>
+        <v>49000</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>1</v>
+        <v>48000</v>
       </c>
       <c r="J79" s="3" t="n">
         <v>0</v>
@@ -5530,33 +5530,29 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>GRINCH ENOJADO, GRICH ENOJADO, SANTA VERDE</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>Disponible en tallas para toda la familia</t>
-        </is>
-      </c>
+          <t>Grinch Enojado, RENO VERDE, RENO BUFANDA, SANTA CARICTURA, SANTA, RENO CUADROS</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uc9c3z0a2am_1791910010182.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nenu0jwquta_1789404771647.webp</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
+          <t>241d370d-0a03-4406-ad18-a9a3755f21cb</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA NAVIDEÑA DE PAREJA</t>
+          <t>PIJAMA NAVIDAD FAMILIAR</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5565,7 +5561,11 @@
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Única, Plus, S, M, L, 2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G80" s="3" t="n">
         <v>3</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -5588,17 +5588,21 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Grinch Enojado, RENO VERDE, RENO BUFANDA, SANTA CARICTURA, SANTA, RENO CUADROS</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>GRINCH ENOJADO, GRICH ENOJADO, SANTA VERDE</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Disponible en tallas para toda la familia</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nenu0jwquta_1789404771647.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uc9c3z0a2am_1791910010182.webp</t>
         </is>
       </c>
       <c r="P80" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -6543,7 +6547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-15 18:30</t>
+          <t>2026-10-16 00:33</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6547,7 +6547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 00:33</t>
+          <t>2026-10-16 06:33</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6547,7 +6547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 06:33</t>
+          <t>2026-10-16 12:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1074,38 +1074,34 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>0ac82993-2a51-4a17-bb30-aff9f190317c</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
+          <t>34a2256f-5327-4fc8-8ab6-0506662828bb</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CAPRI CAMISA PLUS</t>
+          <t>BODDY DE HALLOWEEN</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Capri</t>
+          <t>Body</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>38000</v>
+        <v>28000</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>28000</v>
+        <v>18000</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>27000</v>
+        <v>17000</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0</v>
@@ -1120,37 +1116,37 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>CERDITO, WINE POOH, HELLO KITTY, ELEFANTE, OSO, LOLA, PIOLIN</t>
+          <t>1004165238, 1004165237, 1004165236, 1004165235, 1004165234, 1004165233, 1004165232, 1004165231, 1004165230, 1004165229, 1004165228, 1004165227, 1004165226, 1004165225, 1004165224, 1004165218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS SEDE HASTA UNA XL</t>
+          <t>Talla unica Sedes hasta una talla L</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fl9gpmhi98a_1785464187258.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/j7a765w02fc_1792168079354.webp</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>b5c92717-f48f-48bc-9d14-0ad3a4072983</t>
+          <t>0ac82993-2a51-4a17-bb30-aff9f190317c</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>CCP</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CAPRI TIRAS PLUS</t>
+          <t>CAPRI CAMISA PLUS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1165,14 +1161,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>37000</v>
+        <v>38000</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>26000</v>
-      </c>
       <c r="J11" s="3" t="n">
         <v>0</v>
       </c>
@@ -1186,7 +1182,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>OVEJA NUVE, OSO, DEISY</t>
+          <t>CERDITO, WINE POOH, HELLO KITTY, ELEFANTE, OSO, LOLA, PIOLIN</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1196,27 +1192,27 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/rcy4r0q75fc_1785464406960.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fl9gpmhi98a_1785464187258.webp</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>c92d864d-1944-42a0-b934-5e30d63492b8</t>
+          <t>b5c92717-f48f-48bc-9d14-0ad3a4072983</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CAP-004</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CAPRI CAMISA</t>
+          <t>CAPRI TIRAS PLUS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1227,17 +1223,17 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>34000</v>
+        <v>37000</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1252,17 +1248,17 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA, AVOCADO, CERDITO MORADO</t>
+          <t>OVEJA NUVE, OSO, DEISY</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA PLUS SEDE HASTA UNA XL</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/9fpn02zkhl4_1784909775843.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/rcy4r0q75fc_1785464406960.webp</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
@@ -1272,30 +1268,38 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>bb263b45-9ca5-40e6-ac7b-c4ce91e52caa</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr"/>
+          <t>c92d864d-1944-42a0-b934-5e30d63492b8</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CAP-004</t>
+        </is>
+      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO</t>
+          <t>CAPRI CAMISA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Conjuntos</t>
+          <t>Capri</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
       <c r="G13" s="3" t="n">
-        <v>102000</v>
+        <v>34000</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>92000</v>
+        <v>24000</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>91000</v>
+        <v>23000</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>0</v>
@@ -1310,33 +1314,33 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>BLANCO HUESO, Lila, BLANCO, NEGRO, ROSADO</t>
+          <t>VAQUITA, AVOCADO, CERDITO MORADO</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/oa54xzg5jj_1785464518783.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/9fpn02zkhl4_1784909775843.jpg</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>6a20ef35-5dfe-4005-86f1-b935e730e062</t>
+          <t>bb263b45-9ca5-40e6-ac7b-c4ce91e52caa</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CORSERT CON CORREA</t>
+          <t>CONJUNTO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1345,20 +1349,16 @@
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="3" t="n">
-        <v>101000</v>
+        <v>102000</v>
       </c>
       <c r="H14" s="3" t="n">
+        <v>92000</v>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>91000</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>90000</v>
-      </c>
       <c r="J14" s="3" t="n">
         <v>0</v>
       </c>
@@ -1372,33 +1372,33 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>NEGRO, BEIZ, BLANCO</t>
+          <t>BLANCO HUESO, Lila, BLANCO, NEGRO, ROSADO</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA EN TELA BENGALINA BUENA ENLONGACION</t>
+          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/4tadmh9gyr4_1785265645028.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/oa54xzg5jj_1785464518783.webp</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>e7c38c30-6221-4200-b12f-80e8b13a8d3c</t>
+          <t>6a20ef35-5dfe-4005-86f1-b935e730e062</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO CHALECO MANGA LARGA</t>
+          <t>PANTALON CORSERT CON CORREA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>99000</v>
+        <v>101000</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>89000</v>
+        <v>91000</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>88000</v>
+        <v>90000</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1434,17 +1434,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, NEGRO, BEIGE</t>
+          <t>NEGRO, BEIZ, BLANCO</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA TELA BENGALINA MUY BUENA ENLONGACION</t>
+          <t>TALLA UNICA EN TELA BENGALINA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8wnqa90gpdk_1785260378609.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/4tadmh9gyr4_1785265645028.jpg</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
@@ -1454,13 +1454,13 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>c5b97a84-d8eb-4a14-96a7-2e41d7eb3849</t>
+          <t>e7c38c30-6221-4200-b12f-80e8b13a8d3c</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO ESTRUCTURADO</t>
+          <t>CONJUNTO CHALECO MANGA LARGA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>93000</v>
+        <v>99000</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>83000</v>
+        <v>89000</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>82000</v>
+        <v>88000</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>0</v>
@@ -1496,17 +1496,17 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>BEIZ, NEGRO, BLANCO</t>
+          <t>BLANCO, NEGRO, BEIGE</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA TELA BENGALINA BUENA ENLONGACION</t>
+          <t>TALLA UNICA TELA BENGALINA MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/sk7jlxi3b5_1785266075759.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8wnqa90gpdk_1785260378609.jpg</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
@@ -1516,13 +1516,13 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>296e9fb7-4fe3-48e0-b3e9-60580623eb4e</t>
+          <t>c5b97a84-d8eb-4a14-96a7-2e41d7eb3849</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO ESPALDA DESCOTADA</t>
+          <t>CONJUNTO ESTRUCTURADO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1537,14 +1537,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>92000</v>
+        <v>93000</v>
       </c>
       <c r="H17" s="3" t="n">
+        <v>83000</v>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>82000</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>81000</v>
-      </c>
       <c r="J17" s="3" t="n">
         <v>0</v>
       </c>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/t2nronuzffr_1785266666081.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/sk7jlxi3b5_1785266075759.jpg</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
@@ -1578,13 +1578,13 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>a82d2b7e-06ee-47e6-93b8-2c975b938275</t>
+          <t>296e9fb7-4fe3-48e0-b3e9-60580623eb4e</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CORSET</t>
+          <t>CONJUNTO ESPALDA DESCOTADA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1599,14 +1599,14 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>91000</v>
+        <v>92000</v>
       </c>
       <c r="H18" s="3" t="n">
+        <v>82000</v>
+      </c>
+      <c r="I18" s="3" t="n">
         <v>81000</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>80000</v>
-      </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
       </c>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, BEIZ, NEGRO</t>
+          <t>BEIZ, NEGRO, BLANCO</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/gjenxmmzjml_1785266619593.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/t2nronuzffr_1785266666081.jpg</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
@@ -1640,13 +1640,13 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>641fc2a5-3fca-47be-b968-56f0c908904f</t>
+          <t>a82d2b7e-06ee-47e6-93b8-2c975b938275</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO #406</t>
+          <t>PANTALON CORSET</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>88000</v>
+        <v>91000</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>78000</v>
+        <v>81000</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>77000</v>
+        <v>80000</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>0</v>
@@ -1682,33 +1682,33 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>LILA, ROSADA, AZUL, BLANCO, BLANCO HUESO</t>
+          <t>BLANCO, BEIZ, NEGRO</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
+          <t>TALLA UNICA TELA BENGALINA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/58skqec8s_1785463738920.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/gjenxmmzjml_1785266619593.jpg</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>a338ba30-9646-4d45-9edf-212cba3c2c28</t>
+          <t>641fc2a5-3fca-47be-b968-56f0c908904f</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO MANGA LARGA</t>
+          <t>CONJUNTO #406</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>86000</v>
+        <v>88000</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>76000</v>
+        <v>78000</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>75000</v>
+        <v>77000</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -1744,33 +1744,33 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>LILA, AZUL, NEGRO, ROSADO, BEIZ, BLANCO</t>
+          <t>LILA, ROSADA, AZUL, BLANCO, BLANCO HUESO</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA TELA BURDA ITALIANA BUENA ENLONGACON</t>
+          <t>TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nlt2sqeceem_1785265441199.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/58skqec8s_1785463738920.webp</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>4c63f602-b3d2-422c-bcc9-9b9307477100</t>
+          <t>a338ba30-9646-4d45-9edf-212cba3c2c28</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO CORTE MEDIO</t>
+          <t>CONJUNTO MANGA LARGA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1785,19 +1785,19 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>85000</v>
+        <v>86000</v>
       </c>
       <c r="H21" s="3" t="n">
+        <v>76000</v>
+      </c>
+      <c r="I21" s="3" t="n">
         <v>75000</v>
       </c>
-      <c r="I21" s="3" t="n">
-        <v>74000</v>
-      </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -1806,17 +1806,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>LILA, BLANCO, BEIZ, AZUL AGUAMARINE, ROSADO, NEGRO</t>
+          <t>LILA, AZUL, NEGRO, ROSADO, BEIZ, BLANCO</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA EN TELA ALGODON ITALIANO BUENA ENLONGACION</t>
+          <t>TALLA UNICA TELA BURDA ITALIANA BUENA ENLONGACON</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/z0yy7nfdf3h_1785264862582.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nlt2sqeceem_1785265441199.jpg</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
@@ -1826,13 +1826,13 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>65d17bbf-46cf-4543-9fad-28f1629d162c</t>
+          <t>4c63f602-b3d2-422c-bcc9-9b9307477100</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO #409</t>
+          <t>CONJUNTO CORTE MEDIO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1847,14 +1847,14 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>84000</v>
+        <v>85000</v>
       </c>
       <c r="H22" s="3" t="n">
+        <v>75000</v>
+      </c>
+      <c r="I22" s="3" t="n">
         <v>74000</v>
       </c>
-      <c r="I22" s="3" t="n">
-        <v>73000</v>
-      </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
       </c>
@@ -1868,17 +1868,17 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, AZUL, BEIZ, NEGRO, ROSADO, BLANCO HUESO</t>
+          <t>LILA, BLANCO, BEIZ, AZUL AGUAMARINE, ROSADO, NEGRO</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
+          <t>TALLA UNICA EN TELA ALGODON ITALIANO BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lddsxs7nxfp_1785463564431.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/z0yy7nfdf3h_1785264862582.jpg</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
@@ -1888,13 +1888,13 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>f08b3b26-5b6a-4e81-a679-954fcdf9740a</t>
+          <t>65d17bbf-46cf-4543-9fad-28f1629d162c</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO #403</t>
+          <t>CONJUNTO #409</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>83000</v>
+        <v>84000</v>
       </c>
       <c r="H23" s="3" t="n">
+        <v>74000</v>
+      </c>
+      <c r="I23" s="3" t="n">
         <v>73000</v>
       </c>
-      <c r="I23" s="3" t="n">
-        <v>72000</v>
-      </c>
       <c r="J23" s="3" t="n">
         <v>0</v>
       </c>
@@ -1930,37 +1930,33 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>ROSADO, AZUL, BLANCO, BEIZ, LILA, BLANCO HUESO, NEGRO</t>
+          <t>BLANCO, AZUL, BEIZ, NEGRO, ROSADO, BLANCO HUESO</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
+          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lznznm2o18q_1785463395621.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lddsxs7nxfp_1785463564431.webp</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>fa17b5f9-1f52-45a9-8beb-674c89b950fb</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ECH6875</t>
-        </is>
-      </c>
+          <t>f08b3b26-5b6a-4e81-a679-954fcdf9740a</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO EVILLAS</t>
+          <t>CONJUNTO #403</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1975,19 +1971,19 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>81000</v>
+        <v>83000</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>71000</v>
+        <v>73000</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>70000</v>
+        <v>72000</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -1996,33 +1992,37 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>BEIGE, BLANCO, NEGRO</t>
+          <t>ROSADO, AZUL, BLANCO, BEIZ, LILA, BLANCO HUESO, NEGRO</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>EN TALLA UNICA TELA BENGALINA</t>
+          <t>TALLA UNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ohdoicv47rj_1785260116653.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lznznm2o18q_1785463395621.webp</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>23ef8d15-d448-48d3-91b9-f679d86890c2</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr"/>
+          <t>fa17b5f9-1f52-45a9-8beb-674c89b950fb</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ECH6875</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO #405</t>
+          <t>ENTERIZO EVILLAS</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2037,19 +2037,19 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>75000</v>
+        <v>81000</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>65000</v>
+        <v>71000</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>64000</v>
+        <v>70000</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -2058,33 +2058,33 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>AZUL, BEIZ, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO, ROJO</t>
+          <t>BEIGE, BLANCO, NEGRO</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
+          <t>EN TALLA UNICA TELA BENGALINA</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jv9pucdje5_1785463083571.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ohdoicv47rj_1785260116653.jpg</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>41762a6e-1a11-43c3-be00-7bd9f035a68d</t>
+          <t>23ef8d15-d448-48d3-91b9-f679d86890c2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CONJUNTO TRES CUARTOS</t>
+          <t>CONJUNTO #405</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -2120,42 +2120,38 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>NEGRO, BLANCO HUESO</t>
+          <t>AZUL, BEIZ, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO, ROJO</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA</t>
+          <t>TALLA ÚNICA TELA ALGODON BURDA ITALIANA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l0dlluckb1q_1785265920163.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jv9pucdje5_1785463083571.webp</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>263b9708-cb08-476d-93d8-681becd76643</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>EM-002</t>
-        </is>
-      </c>
+          <t>41762a6e-1a11-43c3-be00-7bd9f035a68d</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO MANGAS</t>
+          <t>CONJUNTO TRES CUARTOS</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Enterizos</t>
+          <t>Conjuntos</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2165,19 +2161,19 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>33000</v>
+        <v>75000</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>22000</v>
+        <v>65000</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>21000</v>
+        <v>64000</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -2186,33 +2182,33 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>BAMBBI, AVOCADO FELIZ, CONEJO, PERRO PUPPY</t>
+          <t>NEGRO, BLANCO HUESO</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>SEDE HASTA UNA TALLA L</t>
+          <t>TALLA ÚNICA</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qoslug987pj_1784921225670.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l0dlluckb1q_1785265920163.jpg</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>9e4cc6dd-dee0-4bc8-971e-0917852ea52b</t>
+          <t>dfc1e5d4-7dd8-40dd-a2da-d0addd10db0d</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO TIRAS NAVIDAD</t>
+          <t>ENTERIZO HALLOWEEN</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2221,15 +2217,19 @@
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
       <c r="G28" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>30000</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>20000</v>
-      </c>
       <c r="I28" s="3" t="n">
-        <v>19000</v>
+        <v>29000</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
@@ -2244,37 +2244,37 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>ARBOLITO, Cuadros rojos</t>
+          <t>SPIDERMAN NEGRO, SPIDERMAN, CAPITAN AMERICA, ESQUELETO, DEPOOL, MUJER MARAVILLA, ESQUELETO CALABAZA, LOS INCREIBLES</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA XL</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/o06mdt8nwsg_1791926907779.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ukhclt1e5cl_1792166421707.webp</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>4e3f5d95-8f05-4444-8008-9e5e08a40abe</t>
+          <t>263b9708-cb08-476d-93d8-681becd76643</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ET-001</t>
+          <t>EM-002</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO TIRA</t>
+          <t>ENTERIZO MANGAS</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0</v>
@@ -2305,38 +2305,38 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>CERDITO</t>
+          <t>BAMBBI, AVOCADO FELIZ, CONEJO, PERRO PUPPY</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO TIRA SEDE HASTA UNA TALLA L</t>
+          <t>SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bw3xibgvppr_1784915289894.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qoslug987pj_1784921225670.jpg</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>79f89726-a52c-4a0a-aef5-b348618f5651</t>
+          <t>9e4cc6dd-dee0-4bc8-971e-0917852ea52b</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ENTERIZO TIRAS</t>
+          <t>ENTERIZO TIRAS NAVIDAD</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2345,19 +2345,15 @@
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="3" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>0</v>
@@ -2372,7 +2368,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>AMARILLO, SALMON, ROSA, ROSADO, AZUL, LILA</t>
+          <t>ARBOLITO, Cuadros rojos</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2382,32 +2378,32 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/f4gcx5fckbl_1785211250771.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/o06mdt8nwsg_1791926907779.webp</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>e9c79d8f-5946-4f21-9571-917d1b04b061</t>
+          <t>4e3f5d95-8f05-4444-8008-9e5e08a40abe</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>PCH-003</t>
+          <t>ET-001</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISA HOMBRE</t>
+          <t>ENTERIZO TIRA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Enterizos</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2417,63 +2413,59 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>41000</v>
+        <v>30000</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>30000</v>
+        <v>19000</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>VEGUETA, PICAPIEDRAS, PADRINO MAGICO, MESSY, MARVEL</t>
+          <t>CERDITO</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA (36)</t>
+          <t>ENTERIZO TIRA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/mn99r1y1ls_1784949944792.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bw3xibgvppr_1784915289894.jpg</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>d408c8d9-4257-4a40-a884-f684922ced46</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>HOM-001</t>
-        </is>
-      </c>
+          <t>79f89726-a52c-4a0a-aef5-b348618f5651</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>BERMUDA HOMBRE</t>
+          <t>ENTERIZO TIRAS</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Enterizos</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2483,13 +2475,13 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>38000</v>
+        <v>27000</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>28000</v>
+        <v>17000</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>27000</v>
+        <v>16000</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -2504,42 +2496,42 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>MICKEY, STICH</t>
+          <t>AMARILLO, SALMON, ROSA, ROSADO, AZUL, LILA</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA SEDE HASTA UNA TALLA (36)</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ya25i5av86q_1784947907589.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/f4gcx5fckbl_1785211250771.jpg</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>f28d98f2-3462-4bbb-97b5-9851c64804bc</t>
+          <t>e9c79d8f-5946-4f21-9571-917d1b04b061</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PJU-005</t>
+          <t>PCH-003</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>PANTALON JUANITA ULICOLOR</t>
+          <t>PANTALON CAMISA HOMBRE</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Juanita</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2549,19 +2541,19 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>32000</v>
+        <v>41000</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>22000</v>
+        <v>31000</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>21000</v>
+        <v>30000</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -2570,38 +2562,42 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO, FLOR, HELLO KITTY AZUL</t>
+          <t>VEGUETA, PICAPIEDRAS, PADRINO MAGICO, MESSY, MARVEL</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA (36)</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fchut0egg2l_1784948160684.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/mn99r1y1ls_1784949944792.jpg</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>929e1473-1c71-4111-be78-4a7e3757a0b2</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr"/>
+          <t>d408c8d9-4257-4a40-a884-f684922ced46</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>HOM-001</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>JUANITA 4 PIEZAS</t>
+          <t>BERMUDA HOMBRE</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Juanita</t>
+          <t>Hombre</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2611,13 +2607,13 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>28000</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>18000</v>
-      </c>
       <c r="I34" s="3" t="n">
-        <v>17000</v>
+        <v>27000</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
@@ -2632,33 +2628,37 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA MORADA, AVOCADO FUCSIA, STICH MORADO, KOALA, OSO LOTSO, MINNIE, CERDITO FUCSIA, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
+          <t>MICKEY, STICH</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>COMPRENDE 4 PIEZAS TALLA UNICA BUENA ENLONGACION</t>
+          <t>TALLA ÚNICA SEDE HASTA UNA TALLA (36)</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqwsrxvr1ic_1789406839500.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ya25i5av86q_1784947907589.jpg</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1fc2c3f6-be41-49b6-a97b-c33cb5933cef</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr"/>
+          <t>f28d98f2-3462-4bbb-97b5-9851c64804bc</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>PJU-005</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>JUANITA SEXY NAVIDAD</t>
+          <t>PANTALON JUANITA ULICOLOR</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2673,13 +2673,13 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>24000</v>
+        <v>32000</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>14000</v>
+        <v>22000</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>13000</v>
+        <v>21000</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
@@ -2694,37 +2694,33 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>SANTA, SANTA CARICATURAS, SANTA TRINEO</t>
+          <t>HELLO KITTY, OSO, FLOR, HELLO KITTY AZUL</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Talla única</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8ny5hos4d9g_1791927026228.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fchut0egg2l_1784948160684.jpg</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>673b49dd-0e8e-4f2a-8e8c-c89494d68101</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>JS107</t>
-        </is>
-      </c>
+          <t>929e1473-1c71-4111-be78-4a7e3757a0b2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>JUANITA SEXY SUBLIMADA</t>
+          <t>JUANITA 4 PIEZAS</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2739,13 +2735,13 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>24000</v>
+        <v>28000</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0</v>
@@ -2760,37 +2756,33 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO, PIOLIN</t>
+          <t>VAQUITA MORADA, AVOCADO FUCSIA, STICH MORADO, KOALA, OSO LOTSO, MINNIE, CERDITO FUCSIA, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>COMPRENDE 4 PIEZAS TALLA UNICA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/45rr6yv31td_1784947244400.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqwsrxvr1ic_1789406839500.webp</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>baef88f3-ffb4-407b-9afd-8f49877f0276</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>JS-003</t>
-        </is>
-      </c>
+          <t>1fc2c3f6-be41-49b6-a97b-c33cb5933cef</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>JUANITA SEXY UNICOLOR</t>
+          <t>JUANITA SEXY NAVIDAD</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2805,19 +2797,19 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -2826,42 +2818,42 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA, OSO TIERNO, MICKEY, STICH, POCHACO, OSO FUCSIA, ESTRELLAS, WINIE POOD, PERRITO, CORAZON LILA, OSO CORAZON, KITTY</t>
+          <t>SANTA, SANTA CARICATURAS, SANTA TRINEO</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>Talla única</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ceffp1umsxh_1784950731524.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8ny5hos4d9g_1791927026228.webp</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>db1b4f39-d39f-4371-8b3b-70ec2153b54f</t>
+          <t>673b49dd-0e8e-4f2a-8e8c-c89494d68101</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>LEV-003</t>
+          <t>JS107</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>LEVANTADORA TRIO</t>
+          <t>JUANITA SEXY SUBLIMADA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Levantadoras</t>
+          <t>Juanita</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2871,13 +2863,13 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>44000</v>
+        <v>24000</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>34000</v>
+        <v>14000</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>33000</v>
+        <v>13000</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>0</v>
@@ -2892,60 +2884,64 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA, OSO DORMILON, POCHACO, AVOCADO FUCSIA, GATA MARIE</t>
+          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO, PIOLIN</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>LEVANTADORA TRIO</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/di0tb0nyeql_1784907641551.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/45rr6yv31td_1784947244400.jpg</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>221b3d57-e2c2-4d8e-b20f-4a227e9675f3</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr"/>
+          <t>baef88f3-ffb4-407b-9afd-8f49877f0276</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>JS-003</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TRIO NIÑAS</t>
+          <t>JUANITA SEXY UNICOLOR</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Juanita</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2/4, 6/8, 10/12, 14/16</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>39000</v>
+        <v>22000</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>29000</v>
+        <v>12000</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>28000</v>
+        <v>12000</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -2954,58 +2950,58 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>CERDITO, STICH, CENICIENTA, AVOCADO</t>
+          <t>VAQUITA, OSO TIERNO, MICKEY, STICH, POCHACO, OSO FUCSIA, ESTRELLAS, WINIE POOD, PERRITO, CORAZON LILA, OSO CORAZON, KITTY</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/imzbzaxzsp_1785213284628.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ceffp1umsxh_1784950731524.jpg</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>8d3a4a02-fe5b-4b4b-bc38-0a105eab5cfb</t>
+          <t>db1b4f39-d39f-4371-8b3b-70ec2153b54f</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PCN</t>
+          <t>LEV-003</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISA NIÑA</t>
+          <t>LEVANTADORA TRIO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Levantadoras</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2/4, 6/8, 10/12, 14/16</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>32000</v>
+        <v>44000</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>22000</v>
+        <v>34000</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>21000</v>
+        <v>33000</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -3020,17 +3016,17 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>cenicienta, Pinguinos, DEISY LILA, STICH, OSA MOÑO</t>
+          <t>VAQUITA, OSO DORMILON, POCHACO, AVOCADO FUCSIA, GATA MARIE</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Disponible en Curva de Tallas</t>
+          <t>LEVANTADORA TRIO</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e3j2zd3xf5o_1789405073203.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/di0tb0nyeql_1784907641551.jpg</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
@@ -3040,17 +3036,13 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>022d6e48-1835-454f-92f8-937c00625ad5</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>BN104</t>
-        </is>
-      </c>
+          <t>221b3d57-e2c2-4d8e-b20f-4a227e9675f3</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA NIÑA</t>
+          <t>PANTALON TRIO NIÑAS</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3065,13 +3057,13 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>27000</v>
+        <v>39000</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>17000</v>
+        <v>29000</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>16000</v>
+        <v>28000</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0</v>
@@ -3086,7 +3078,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>BULMA, BOB ESPONJA, OSO, PAYASITO, PINGUINO, OVEJA, WINNE POOH, ARIEL, GATA HUELLAS, OSA, CONEJO ESTRELLAS</t>
+          <t>CERDITO, STICH, CENICIENTA, AVOCADO</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3096,27 +3088,27 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qrm1cm85f6_1789405836874.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/imzbzaxzsp_1785213284628.jpg</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>b83bfa51-838e-4d72-8107-300660806c65</t>
+          <t>8d3a4a02-fe5b-4b4b-bc38-0a105eab5cfb</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BN102</t>
+          <t>PCN</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>BATOLA NIÑA</t>
+          <t>PANTALON CAMISA NIÑA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3125,15 +3117,19 @@
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G42" s="3" t="n">
-        <v>25000</v>
+        <v>32000</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>14000</v>
+        <v>21000</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>0</v>
@@ -3146,36 +3142,44 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>cenicienta, Pinguinos, DEISY LILA, STICH, OSA MOÑO</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>TALLAS 2/4-6/8-10/12-14/16 TALLAJE NORMAL</t>
+          <t>Disponible en Curva de Tallas</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/b0oc4bgkm8b_1784915527640.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e3j2zd3xf5o_1789405073203.webp</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>616e6657-708b-474d-888b-b1752a032f5b</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
+          <t>022d6e48-1835-454f-92f8-937c00625ad5</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>BN104</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TRIO DE NIÑOS</t>
+          <t>SHORT CAMISA NIÑA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -3185,13 +3189,13 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>39000</v>
+        <v>27000</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>28000</v>
+        <v>16000</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>0</v>
@@ -3206,58 +3210,54 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>POKEMON, TOY STORY, CARS, DIONOSAURIO, CAPIBARA, GOKU, DEMON SKAYER, IROMAN, ONE PIECE, BATMAN</t>
+          <t>BULMA, BOB ESPONJA, OSO, PAYASITO, PINGUINO, OVEJA, WINNE POOH, ARIEL, GATA HUELLAS, OSA, CONEJO ESTRELLAS</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>CLMPRENDE TRES PIEZAS DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
+          <t>DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/g983o9wjbmm_1785213690452.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qrm1cm85f6_1789405836874.webp</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2f708066-5d01-4a63-aa7f-a66ca37719f9</t>
+          <t>b83bfa51-838e-4d72-8107-300660806c65</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PN101</t>
+          <t>BN102</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISA NIÑO</t>
+          <t>BATOLA NIÑA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>2/4, 6/8, 10/12, 14/16</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="3" t="n">
-        <v>32000</v>
+        <v>25000</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>0</v>
@@ -3270,39 +3270,31 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>CAPITAN AMERICA, IROMAN, AVENGERS, BARTS, STICH, CAPITAN AMERICA BLANCO, BATMAN, BARTS SIMSOMP, NARUTO</t>
-        </is>
-      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLE EN CURVA DE TALLAS TALLAJE NORMAL</t>
+          <t>TALLAS 2/4-6/8-10/12-14/16 TALLAJE NORMAL</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/m8a6el1a9h_1785205682420.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/b0oc4bgkm8b_1784915527640.jpg</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>49a86fb8-53e6-4339-9ffd-4aa3ce6873a5</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>BCN</t>
-        </is>
-      </c>
+          <t>616e6657-708b-474d-888b-b1752a032f5b</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>BERMUDA CAMISA NIÑO</t>
+          <t>PANTALON TRIO DE NIÑOS</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3317,14 +3309,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
+        <v>39000</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>29000</v>
+      </c>
+      <c r="I45" s="3" t="n">
         <v>28000</v>
       </c>
-      <c r="H45" s="3" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>17000</v>
-      </c>
       <c r="J45" s="3" t="n">
         <v>0</v>
       </c>
@@ -3338,58 +3330,58 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>STICH, SIMPSON, MICKEY, BOB ESPONJA, GOKU, IROMAN, DINO, SPAIDERMAN, MICKEY NEGRO, PICAPIEDRAS, SONNY</t>
+          <t>POKEMON, TOY STORY, CARS, DIONOSAURIO, CAPIBARA, GOKU, DEMON SKAYER, IROMAN, ONE PIECE, BATMAN</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLE EN CURVA COMPLETA BUENA ENLONGACION</t>
+          <t>CLMPRENDE TRES PIEZAS DISPONIBLE EN TALLAS 2/4 6/8 10/12</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l7lomlcb9s_1789405548938.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/g983o9wjbmm_1785213690452.jpg</t>
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>4d530fc3-f6e4-4f32-a352-7a41bf6e548a</t>
+          <t>2f708066-5d01-4a63-aa7f-a66ca37719f9</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PAD-004</t>
+          <t>PN101</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISERA DAMA</t>
+          <t>PANTALON CAMISA NIÑO</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Pantalones Dama</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>2/4, 6/8, 10/12, 14/16</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>0</v>
@@ -3404,54 +3396,58 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>OVEJA NUBE, STAR WARS, SIMSOMPS</t>
+          <t>CAPITAN AMERICA, IROMAN, AVENGERS, BARTS, STICH, CAPITAN AMERICA BLANCO, BATMAN, BARTS SIMSOMP, NARUTO</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>DISPONIBLE EN CURVA DE TALLAS TALLAJE NORMAL</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/soebsoaf9a_1784923641827.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/m8a6el1a9h_1785205682420.jpg</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>b76e12a6-9971-4f97-99a1-914753584349</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr"/>
+          <t>49a86fb8-53e6-4339-9ffd-4aa3ce6873a5</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>BCN</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>PANTALON COQUETA TANGA</t>
+          <t>BERMUDA CAMISA NIÑO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Pantalones Dama</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>2/4, 6/8, 10/12, 14/16</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>39000</v>
+        <v>28000</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>29000</v>
+        <v>18000</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>28000</v>
+        <v>17000</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>0</v>
@@ -3466,37 +3462,37 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>PIOLIN, GATO ROSA, MY MELODDY, OSA CORAZONES, AVOCADO</t>
+          <t>STICH, SIMPSON, MICKEY, BOB ESPONJA, GOKU, IROMAN, DINO, SPAIDERMAN, MICKEY NEGRO, PICAPIEDRAS, SONNY</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>TALLA ÚNICA COMPRENDE TRES PIEZAS</t>
+          <t>DISPONIBLE EN CURVA COMPLETA BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/76efmc2g288_1791399661792.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l7lomlcb9s_1789405548938.webp</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>a33b8c41-afe2-4d95-b3cf-e3d852124a09</t>
+          <t>4d530fc3-f6e4-4f32-a352-7a41bf6e548a</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>PBT</t>
+          <t>PAD-004</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>PANTALON BOLERO TANGA.</t>
+          <t>SHORT CAMISERA DAMA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3511,14 +3507,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>39000</v>
+        <v>40000</v>
       </c>
       <c r="H48" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I48" s="3" t="n">
         <v>29000</v>
       </c>
-      <c r="I48" s="3" t="n">
-        <v>28000</v>
-      </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
       </c>
@@ -3532,37 +3528,33 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>LOTTSO, 101 DALMATA, BURBUJA, CINAMORROL, MINNIE, KITTY, STICH MORADO, 1003733655, MICKEY, POCHACO, CAPIBARA</t>
+          <t>OVEJA NUBE, STAR WARS, SIMSOMPS</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Comprede 3 Piezas Talla Única Sede hasta una talla L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lztijdyhzrr_1787193266433.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/soebsoaf9a_1784923641827.jpg</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>9db66764-f682-4f29-9f2a-74120a6bfbda</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>PMLD</t>
-        </is>
-      </c>
+          <t>b76e12a6-9971-4f97-99a1-914753584349</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>PANTALON MANGA LARGA DAMA</t>
+          <t>PANTALON COQUETA TANGA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3598,37 +3590,37 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>GATA MARIE, GARFIEL, CINAMORROL, OSO LILA, MINNIE ROJA, PIOLIN</t>
+          <t>PIOLIN, GATO ROSA, MY MELODDY, OSA CORAZONES, AVOCADO</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA MUY BUENA ENLONGACION</t>
+          <t>TALLA ÚNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/z62o4q4ky7d_1786225187133.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/76efmc2g288_1791399661792.webp</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>888e5349-d67e-4fde-896a-d73c72e01c44</t>
+          <t>a33b8c41-afe2-4d95-b3cf-e3d852124a09</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>PET-</t>
+          <t>PBT</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TOP ESQUELETO</t>
+          <t>PANTALON BOLERO TANGA.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3664,37 +3656,37 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>CERDITO</t>
+          <t>LOTTSO, 101 DALMATA, BURBUJA, CINAMORROL, MINNIE, KITTY, STICH MORADO, 1003733655, MICKEY, POCHACO, CAPIBARA</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
+          <t>Comprede 3 Piezas Talla Única Sede hasta una talla L</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8n2pel9plzr_1785210700469.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lztijdyhzrr_1787193266433.webp</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>5192e31f-5f3e-420f-86fa-171d093d3d12</t>
+          <t>9db66764-f682-4f29-9f2a-74120a6bfbda</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PTP-003</t>
+          <t>PMLD</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TIRA PLUS</t>
+          <t>PANTALON MANGA LARGA DAMA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3705,7 +3697,7 @@
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
@@ -3730,37 +3722,37 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>ANGELICA, MINNIE ROJA, OSSO, DONALD, ALADDINO, SNOOPY, VAQUITA MOO, PINGUINOS, PLUTTO, KOALA, PANTERA ROSA, GARFIEL, STICH, TIGERS, BOB ESPONJA</t>
+          <t>GATA MARIE, GARFIEL, CINAMORROL, OSO LILA, MINNIE ROJA, PIOLIN</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS SEDE PARA UNA TALLA XL</t>
+          <t>TALLA UNICA MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3z8ms0l7vdp_1784912750113.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/z62o4q4ky7d_1786225187133.webp</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1604c1b6-9de6-4f63-86ad-974f776ecef0</t>
+          <t>888e5349-d67e-4fde-896a-d73c72e01c44</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PCD103</t>
+          <t>PET-</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISETA</t>
+          <t>PANTALON TOP ESQUELETO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3775,13 +3767,13 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>36000</v>
+        <v>39000</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="J52" s="3" t="n">
         <v>0</v>
@@ -3796,37 +3788,37 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>CARLITOS, CERDITO, CHIMUELO, PIOLIN, VAQUITA, KOALA, PLUTO, CAPIBARA FLOR, STICH FUEGO, OSO LOTTSO, BOB ESPONJA, MICKEY DORMILON, JIRAFFA</t>
+          <t>CERDITO</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lvax3vg7hag_1784914577547.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8n2pel9plzr_1785210700469.jpg</t>
         </is>
       </c>
       <c r="P52" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>83ebf033-cb6e-4a1c-a85b-7835f122ea37</t>
+          <t>5192e31f-5f3e-420f-86fa-171d093d3d12</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>PAD-001</t>
+          <t>PTP-003</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TIRAS</t>
+          <t>PANTALON TIRA PLUS</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3837,17 +3829,17 @@
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>34000</v>
+        <v>39000</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>24000</v>
+        <v>29000</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>23000</v>
+        <v>28000</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>0</v>
@@ -3862,37 +3854,37 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, HELLO KITTY, PATO DONALD</t>
+          <t>ANGELICA, MINNIE ROJA, OSSO, DONALD, ALADDINO, SNOOPY, VAQUITA MOO, PINGUINOS, PLUTTO, KOALA, PANTERA ROSA, GARFIEL, STICH, TIGERS, BOB ESPONJA</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA PLUS SEDE PARA UNA TALLA XL</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lzr466vorq_1784912376517.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3z8ms0l7vdp_1784912750113.jpg</t>
         </is>
       </c>
       <c r="P53" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>05c6ee82-8ae3-4399-8b67-fade58b8d79d</t>
+          <t>1604c1b6-9de6-4f63-86ad-974f776ecef0</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>PCDM-</t>
+          <t>PCD103</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CORTE MEDIO</t>
+          <t>PANTALON CAMISETA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3907,13 +3899,13 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>22000</v>
+        <v>25000</v>
       </c>
       <c r="J54" s="3" t="n">
         <v>0</v>
@@ -3928,42 +3920,42 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>STICH</t>
+          <t>CARLITOS, CERDITO, CHIMUELO, PIOLIN, VAQUITA, KOALA, PLUTO, CAPIBARA FLOR, STICH FUEGO, OSO LOTTSO, BOB ESPONJA, MICKEY DORMILON, JIRAFFA</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/69jr9dn9xjk_1785210970260.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lvax3vg7hag_1784914577547.jpg</t>
         </is>
       </c>
       <c r="P54" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23ab5a86-3b70-45bc-914b-9af5b5a8e85e</t>
+          <t>83ebf033-cb6e-4a1c-a85b-7835f122ea37</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>PNK-001</t>
+          <t>PAD-001</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PINK</t>
+          <t>PANTALON TIRAS</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Pantalones Dama</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3973,13 +3965,13 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>28000</v>
+        <v>34000</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="J55" s="3" t="n">
         <v>0</v>
@@ -3994,7 +3986,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE, HELLO KITTY</t>
+          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, HELLO KITTY, PATO DONALD</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4004,44 +3996,48 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/v0krnzso3j_1784948725231.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lzr466vorq_1784912376517.jpg</t>
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>fb84d852-bf79-4573-9986-2533fee9e7e1</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr"/>
+          <t>05c6ee82-8ae3-4399-8b67-fade58b8d79d</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>PCDM-</t>
+        </is>
+      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SET LUPITA</t>
+          <t>PANTALON CORTE MEDIO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
+          <t>Pantalones Dama</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>S, M, L</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>46000</v>
+        <v>33000</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>36000</v>
+        <v>23000</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>35000</v>
+        <v>22000</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>0</v>
@@ -4056,54 +4052,58 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, VINOTINTO, ROJO</t>
+          <t>STICH</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>ESTILO CORSET TALLAS S-M-L</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ep029rxa8a9_1785718833355.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/69jr9dn9xjk_1785210970260.jpg</t>
         </is>
       </c>
       <c r="P56" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>e78bc16f-eb3a-4579-a9c0-5ba22019056c</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr"/>
+          <t>23ab5a86-3b70-45bc-914b-9af5b5a8e85e</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>PNK-001</t>
+        </is>
+      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SET CRETA</t>
+          <t>PIJAMA PINK</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>S, M, L</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>46000</v>
+        <v>28000</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>35000</v>
+        <v>17000</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>0</v>
@@ -4118,33 +4118,33 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, NEGRO, ROJO</t>
+          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE, HELLO KITTY</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>TALLAS S-M-L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/6bowpox83om_1785716981956.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/v0krnzso3j_1784948725231.jpg</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2d1bb0dc-e10e-4125-8a8a-9b290bc8dea2</t>
+          <t>fb84d852-bf79-4573-9986-2533fee9e7e1</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>SET AURORA</t>
+          <t>SET LUPITA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4180,33 +4180,33 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>ROJO, NEGRO, BLANCO, VINOTINTO</t>
+          <t>BLANCO, VINOTINTO, ROJO</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>TALLAS S-M-L</t>
+          <t>ESTILO CORSET TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cw351gdhp9w_1785716795373.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ep029rxa8a9_1785718833355.webp</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>f6a756c1-e2a7-4de1-bf68-95fc2bcb6eab</t>
+          <t>e78bc16f-eb3a-4579-a9c0-5ba22019056c</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SET CARTAGENA</t>
+          <t>SET CRETA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>NEGRO, ROJO, LILA, BLANCO</t>
+          <t>BLANCO, NEGRO, ROJO</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4252,23 +4252,23 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fu0o9sy5kv9_1785716248806.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/6bowpox83om_1785716981956.webp</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>6e456677-4e39-4c60-9f88-4bac91698de5</t>
+          <t>2d1bb0dc-e10e-4125-8a8a-9b290bc8dea2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>SET LINA</t>
+          <t>SET AURORA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4283,14 +4283,14 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>45000</v>
+        <v>46000</v>
       </c>
       <c r="H60" s="3" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I60" s="3" t="n">
         <v>35000</v>
       </c>
-      <c r="I60" s="3" t="n">
-        <v>34000</v>
-      </c>
       <c r="J60" s="3" t="n">
         <v>0</v>
       </c>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>CON VARILLA EN TALLAS S-M-L</t>
+          <t>TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hd7g4iuoebj_1785718550142.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cw351gdhp9w_1785716795373.webp</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
@@ -4324,13 +4324,13 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>c5494a8f-584c-4533-b646-be158b96c3f9</t>
+          <t>f6a756c1-e2a7-4de1-bf68-95fc2bcb6eab</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>SET TANGA TRANSPARENTE</t>
+          <t>SET CARTAGENA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4345,13 +4345,13 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>37000</v>
+        <v>46000</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>26000</v>
+        <v>35000</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>BLANCO, NEGRO, ROJO</t>
+          <t>NEGRO, ROJO, LILA, BLANCO</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4376,23 +4376,23 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hr2yhxmvdc_1785716489297.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/fu0o9sy5kv9_1785716248806.webp</t>
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>10aa3e72-f092-4927-9f1e-9bd87f1b00b4</t>
+          <t>6e456677-4e39-4c60-9f88-4bac91698de5</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>SET PARIS</t>
+          <t>SET LINA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4407,13 +4407,13 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>33000</v>
+        <v>45000</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>23000</v>
+        <v>35000</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>22000</v>
+        <v>34000</v>
       </c>
       <c r="J62" s="3" t="n">
         <v>0</v>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>VINOTINTO, BLANCO, NEGRO, ROJO</t>
+          <t>ROJO, NEGRO, BLANCO, VINOTINTO</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>TALLAS S-M-L</t>
+          <t>CON VARILLA EN TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/0pluslhpj7m_1785717182849.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hd7g4iuoebj_1785718550142.webp</t>
         </is>
       </c>
       <c r="P62" s="2" t="n">
@@ -4448,44 +4448,40 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>c98f7973-6d9d-4604-a2a0-8b7e6b47c42d</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SCD</t>
-        </is>
-      </c>
+          <t>c5494a8f-584c-4533-b646-be158b96c3f9</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISERA PLUS</t>
+          <t>SET TANGA TRANSPARENTE</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Short Dama</t>
+          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>S, M, L</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>44000</v>
+        <v>37000</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>34000</v>
+        <v>27000</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="J63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -4494,54 +4490,54 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>OJOS, MINNIE, HELLO KITTY, OSO PANDA, STICH</t>
+          <t>BLANCO, NEGRO, ROJO</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS</t>
+          <t>TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l8f7zp228yi_1785250753887.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/hr2yhxmvdc_1785716489297.webp</t>
         </is>
       </c>
       <c r="P63" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ee0c9e00-4ef6-49e8-bd0c-cc4658163c4a</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>PS-0532</t>
-        </is>
-      </c>
+          <t>10aa3e72-f092-4927-9f1e-9bd87f1b00b4</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA EN SATIN</t>
+          <t>SET PARIS</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Short Dama</t>
+          <t xml:space="preserve">ROPA INTERIOR DAMA </t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>S, M, L</t>
+        </is>
+      </c>
       <c r="G64" s="3" t="n">
-        <v>34000</v>
+        <v>33000</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4556,37 +4552,37 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>VINOTINTO, BLANCO, NEGRO, ROJO</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>TALLAS M/L L/XL</t>
+          <t>TALLAS S-M-L</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/xd9j7q8l55_1785211668886.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/0pluslhpj7m_1785717182849.webp</t>
         </is>
       </c>
       <c r="P64" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>167648e0-7d81-42c8-82a1-56eb76230f9c</t>
+          <t>c98f7973-6d9d-4604-a2a0-8b7e6b47c42d</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SCO-005</t>
+          <t>SCD</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA OVERSIZE</t>
+          <t>SHORT CAMISERA PLUS</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4597,23 +4593,23 @@
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Oversize</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>32000</v>
+        <v>44000</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>22000</v>
+        <v>34000</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>21000</v>
+        <v>33000</v>
       </c>
       <c r="J65" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -4622,17 +4618,17 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>LABUBU, STICH, GATA MARIE, CERDITO, AVOCADO</t>
+          <t>OJOS, MINNIE, HELLO KITTY, OSO PANDA, STICH</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA ESTILO OVERSIZE</t>
+          <t>TALLA PLUS</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/zt0i4vuxg2q_1784924942802.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/l8f7zp228yi_1785250753887.jpg</t>
         </is>
       </c>
       <c r="P65" s="2" t="n">
@@ -4642,17 +4638,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
+          <t>ee0c9e00-4ef6-49e8-bd0c-cc4658163c4a</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SET104</t>
+          <t>PS-0532</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>PIJAMA EN SATIN</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4661,19 +4657,15 @@
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="3" t="n">
-        <v>30000</v>
+        <v>34000</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="J66" s="3" t="n">
         <v>0</v>
@@ -4688,37 +4680,37 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>TALLAS M/L L/XL</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/xd9j7q8l55_1785211668886.jpg</t>
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
+          <t>167648e0-7d81-42c8-82a1-56eb76230f9c</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>STP-002</t>
+          <t>SCO-005</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS</t>
+          <t>SHORT CAMISA OVERSIZE</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4729,17 +4721,17 @@
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Oversize</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>30000</v>
+        <v>32000</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0</v>
@@ -4754,33 +4746,37 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1003145115, RULERGS, OSO ANTIFAZ, COFFE, PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>LABUBU, STICH, GATA MARIE, CERDITO, AVOCADO</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
+          <t>TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/q027f72zlv8_1784914996896.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/zt0i4vuxg2q_1784924942802.jpg</t>
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>db868027-05ab-43da-b546-090a8bfb7db5</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr"/>
+          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SET104</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA DAMA</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4795,13 +4791,13 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0</v>
@@ -4816,37 +4812,37 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>BOB ESPONJA, MICKEY, AVOCADO</t>
+          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/66paf71xy1x_1785211377717.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>7596d757-8fa0-4cfa-b1ea-05020cf6576d</t>
+          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>SL-006</t>
+          <t>STP-002</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SHORT LOLITA</t>
+          <t>SHORT TIRA PLUS</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4857,14 +4853,14 @@
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>19000</v>
@@ -4882,33 +4878,33 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>MICKEY, VAQUITA, AVOCADO, STICH</t>
+          <t>1003145115, RULERGS, OSO ANTIFAZ, COFFE, PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/03pl1niffof5_1784948410390.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/q027f72zlv8_1784914996896.jpg</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>1c07b490-194e-4d0d-9b23-8db44a3074eb</t>
+          <t>db868027-05ab-43da-b546-090a8bfb7db5</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>SHORT COQUETA</t>
+          <t>SHORT CAMISA DAMA</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4923,14 +4919,14 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="H70" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I70" s="3" t="n">
         <v>17000</v>
       </c>
-      <c r="I70" s="3" t="n">
-        <v>16000</v>
-      </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
       </c>
@@ -4944,37 +4940,37 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>COME GALLETA, MICKEY, MINNIE, POCHACO</t>
+          <t>BOB ESPONJA, MICKEY, AVOCADO</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ttnjnuimxyk_1785213579780.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/66paf71xy1x_1785211377717.jpg</t>
         </is>
       </c>
       <c r="P70" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>0d91b05e-0729-4465-b113-6a4d889a4bf7</t>
+          <t>7596d757-8fa0-4cfa-b1ea-05020cf6576d</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>JSP-008</t>
+          <t>SL-006</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>SHORT JUANITA PLUS</t>
+          <t>SHORT LOLITA</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4985,17 +4981,17 @@
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
@@ -5010,38 +5006,38 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>BURBUJA, MY MELODDI, DEISY, OSO, PIOLIN, JIRAFA</t>
+          <t>MICKEY, VAQUITA, AVOCADO, STICH</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS SEDE HASTA UNA XL MUY BUENA ENLONGACION</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqtwgozcis_1785000102336.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/03pl1niffof5_1784948410390.jpg</t>
         </is>
       </c>
       <c r="P71" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>12c5e812-44c1-40ac-baec-0f01c893b373</t>
+          <t>1c07b490-194e-4d0d-9b23-8db44a3074eb</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CHAQUETA ANTIFLUIDO</t>
+          <t>SHORT COQUETA</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Sin categoría</t>
+          <t>Short Dama</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -5051,13 +5047,13 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>40000</v>
+        <v>27000</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>30000</v>
+        <v>17000</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>29000</v>
+        <v>16000</v>
       </c>
       <c r="J72" s="3" t="n">
         <v>0</v>
@@ -5072,58 +5068,58 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>TOTTO, WINNE POOH, WINNE POOH LILA</t>
+          <t>COME GALLETA, MICKEY, MINNIE, POCHACO</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bbfyrwx0vfu_1785213166473.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ttnjnuimxyk_1785213579780.jpg</t>
         </is>
       </c>
       <c r="P72" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>a687b655-eda4-4a0d-83f4-5d6ea274e2aa</t>
+          <t>0d91b05e-0729-4465-b113-6a4d889a4bf7</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SCO</t>
+          <t>JSP-008</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA OVERSIZE UNICOLOR</t>
+          <t>SHORT JUANITA PLUS</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Sin categoría</t>
+          <t>Short Dama</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="J73" s="3" t="n">
         <v>0</v>
@@ -5138,58 +5134,54 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>BEIZ, ROJO, SALMÓN, AMARILLO, FUCSIA, NEGRO, AZUL, ROSADO</t>
+          <t>BURBUJA, MY MELODDI, DEISY, OSO, PIOLIN, JIRAFA</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA ESTILO OVERSIZE</t>
+          <t>TALLA PLUS SEDE HASTA UNA XL MUY BUENA ENLONGACION</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/38qfshu6kkf_1785211937680.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqtwgozcis_1785000102336.jpg</t>
         </is>
       </c>
       <c r="P73" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>050b8c7d-3cbf-42f4-954e-3c74521decc0</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
+          <t>12c5e812-44c1-40ac-baec-0f01c893b373</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA TRIO PAREJA</t>
+          <t>CHAQUETA ANTIFLUIDO</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Trios</t>
+          <t>Sin categoría</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>94000</v>
+        <v>40000</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>74000</v>
+        <v>30000</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>72000</v>
+        <v>29000</v>
       </c>
       <c r="J74" s="3" t="n">
         <v>0</v>
@@ -5204,58 +5196,58 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1003558423, 1003558424, 1003558425, 1003558426, 1003558427</t>
+          <t>TOTTO, WINNE POOH, WINNE POOH LILA</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/tjxjxutxyaj_1785205292625.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/bbfyrwx0vfu_1785213166473.jpg</t>
         </is>
       </c>
       <c r="P74" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>636942f3-00d7-402f-95bb-ad8a4cfc82ce</t>
+          <t>a687b655-eda4-4a0d-83f4-5d6ea274e2aa</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>PTP-002</t>
+          <t>SCO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>PANTALON TRIO PLUS</t>
+          <t>SHORT CAMISA OVERSIZE UNICOLOR</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Trios</t>
+          <t>Sin categoría</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>48000</v>
+        <v>30000</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>38000</v>
+        <v>20000</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>37000</v>
+        <v>19000</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0</v>
@@ -5270,37 +5262,37 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, DEISY, CAPIBARA, MINNIE, MAFALDA, OVEJA NUBE, AVOCADO, OSO BEARS, BETYU BOOP, SHICH, PANTERA ROSA</t>
+          <t>BEIZ, ROJO, SALMÓN, AMARILLO, FUCSIA, NEGRO, AZUL, ROSADO</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>TALLA PLUS COMPRENDE 3 PIEZAS SEDE HASTA UNA XL</t>
+          <t>TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3ccjn2e0yqn_1785010981212.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/38qfshu6kkf_1785211937680.jpg</t>
         </is>
       </c>
       <c r="P75" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>88515395-2f66-4a68-9d2b-2f598f2a9386</t>
+          <t>050b8c7d-3cbf-42f4-954e-3c74521decc0</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>TRI-005</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>TRIO OVERSIZE DAMA</t>
+          <t>PIJAMA TRIO PAREJA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5315,13 +5307,13 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>44000</v>
+        <v>94000</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>34000</v>
+        <v>74000</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>33000</v>
+        <v>72000</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0</v>
@@ -5336,37 +5328,37 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
+          <t>1003558423, 1003558424, 1003558425, 1003558426, 1003558427</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>COMPRENDE 3 PIEZAS TALLA UNICA ESTILO OVERSIZE</t>
+          <t>TALLA UNICA COMPRENDE TRES PIEZAS</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e0wxiek6bya_1784951657522.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/tjxjxutxyaj_1785205292625.jpg</t>
         </is>
       </c>
       <c r="P76" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>c0e4735f-c320-4741-a9d0-d2c37f06b00e</t>
+          <t>636942f3-00d7-402f-95bb-ad8a4cfc82ce</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>TRI-004</t>
+          <t>PTP-002</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>PANTALON LOLITA</t>
+          <t>PANTALON TRIO PLUS</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5377,17 +5369,17 @@
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H77" s="3" t="n">
         <v>38000</v>
       </c>
-      <c r="H77" s="3" t="n">
-        <v>28000</v>
-      </c>
       <c r="I77" s="3" t="n">
-        <v>27000</v>
+        <v>37000</v>
       </c>
       <c r="J77" s="3" t="n">
         <v>0</v>
@@ -5402,58 +5394,58 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>MINNIE, DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
+          <t>HELLO KITTY, DEISY, CAPIBARA, MINNIE, MAFALDA, OVEJA NUBE, AVOCADO, OSO BEARS, BETYU BOOP, SHICH, PANTERA ROSA</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>COMPRENDE TRES PIEZAS SEDE HASTA UNA TALLA L</t>
+          <t>TALLA PLUS COMPRENDE 3 PIEZAS SEDE HASTA UNA XL</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/njirlp0s9_1784991741310.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/3ccjn2e0yqn_1785010981212.jpg</t>
         </is>
       </c>
       <c r="P77" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>514e5dfc-3d76-4103-be01-5a67ca1668a5</t>
+          <t>88515395-2f66-4a68-9d2b-2f598f2a9386</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>VES-001</t>
+          <t>TRI-005</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VESTIDO MOSCHINO</t>
+          <t>TRIO OVERSIZE DAMA</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Vestidos</t>
+          <t>Trios</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Oversize</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>36000</v>
+        <v>44000</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>26000</v>
+        <v>34000</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>25000</v>
+        <v>33000</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>0</v>
@@ -5468,17 +5460,17 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>GALFIER, DONALD, BOB ESPONJA, STICH, ANGELICA, HELLO KITTY</t>
+          <t>OSO LOTSO, POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>COMPRENDE 3 PIEZAS TALLA UNICA ESTILO OVERSIZE</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxvkwf1vifk_1784950374041.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e0wxiek6bya_1784951657522.jpg</t>
         </is>
       </c>
       <c r="P78" s="2" t="n">
@@ -5488,18 +5480,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr"/>
+          <t>c0e4735f-c320-4741-a9d0-d2c37f06b00e</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>TRI-004</t>
+        </is>
+      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA NAVIDEÑA DE PAREJA</t>
+          <t>PANTALON LOLITA</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>familiar</t>
+          <t>Trios</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -5509,13 +5505,13 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>59000</v>
+        <v>38000</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>49000</v>
+        <v>28000</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>48000</v>
+        <v>27000</v>
       </c>
       <c r="J79" s="3" t="n">
         <v>0</v>
@@ -5530,50 +5526,58 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Grinch Enojado, RENO VERDE, RENO BUFANDA, SANTA CARICTURA, SANTA, RENO CUADROS</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>MINNIE, DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>COMPRENDE TRES PIEZAS SEDE HASTA UNA TALLA L</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nenu0jwquta_1789404771647.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/njirlp0s9_1784991741310.jpg</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>241d370d-0a03-4406-ad18-a9a3755f21cb</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr"/>
+          <t>514e5dfc-3d76-4103-be01-5a67ca1668a5</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>VES-001</t>
+        </is>
+      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA NAVIDAD FAMILIAR</t>
+          <t>VESTIDO MOSCHINO</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>familiar</t>
+          <t>Vestidos</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, S, M, L, 2/4, 6/8, 10/12, 14/16</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1</v>
+        <v>25000</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>0</v>
@@ -5588,33 +5592,33 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>GRINCH ENOJADO, GRICH ENOJADO, SANTA VERDE</t>
+          <t>GALFIER, DONALD, BOB ESPONJA, STICH, ANGELICA, HELLO KITTY</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Disponible en tallas para toda la familia</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uc9c3z0a2am_1791910010182.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxvkwf1vifk_1784950374041.jpg</t>
         </is>
       </c>
       <c r="P80" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ffc59a3f-0bbb-4c8e-8f5a-dc6478217e7e</t>
+          <t>930d9a47-1c0a-4813-81a5-dee51ccc96be</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>PIJAMAS FAMILIARES</t>
+          <t>PIJAMA NAVIDEÑA DE PAREJA</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5623,17 +5627,25 @@
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
       <c r="G81" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
+        <v>59000</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>49000</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>48000</v>
+      </c>
       <c r="J81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
@@ -5642,33 +5654,29 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>FAMILIA SIMPSONS, FAMILIA STICH, FAMILIA AVENGERS, FAMILIA IROMAN, FAMILIA CAPITAN AMERICA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>DISPONIBLES PARA TODA LA FAMILIA</t>
-        </is>
-      </c>
+          <t>Grinch Enojado, RENO VERDE, RENO BUFANDA, SANTA CARICTURA, SANTA, RENO CUADROS</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/iorl7i3h4x_1785715610130.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/nenu0jwquta_1789404771647.webp</t>
         </is>
       </c>
       <c r="P81" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>35feb43b-d4ee-4cd0-97a4-a6461daee102</t>
+          <t>241d370d-0a03-4406-ad18-a9a3755f21cb</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA FAMILIAR NAVIDEÑAS</t>
+          <t>PIJAMA NAVIDAD FAMILIAR</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5677,7 +5685,11 @@
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Única, Plus, S, M, L, 2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G82" s="3" t="n">
         <v>3</v>
       </c>
@@ -5691,7 +5703,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
@@ -5700,64 +5712,52 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Grinch Enojado, Reno Nuevo, Santa y Mickey, Papá Noel reno, Santa Nieve, STICH, MICKEY, STICH ROJO, GRINCH ARBOLITO, STICH AZUL, MICKEY ROJO, MICKEY ARBOLITO, STICH BLANCO</t>
+          <t>GRINCH ENOJADO, GRICH ENOJADO, SANTA VERDE</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>DISPONIBLES EN TALLAS PARA TODA LA FAMILIA</t>
+          <t>Disponible en tallas para toda la familia</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uo66j97t3qc_1789404070898.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uc9c3z0a2am_1791910010182.webp</t>
         </is>
       </c>
       <c r="P82" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>237051ec-4251-4654-9e91-8b031dd0ac56</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>HOM-002</t>
-        </is>
-      </c>
+          <t>ffc59a3f-0bbb-4c8e-8f5a-dc6478217e7e</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>PANTALON CAMISERA PAREJA</t>
+          <t>PIJAMAS FAMILIARES</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>pijama-pareja</t>
+          <t>familiar</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="3" t="n">
-        <v>95000</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>73000</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
       <c r="J83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -5766,60 +5766,56 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>BATMAN, STAR WARS</t>
+          <t>FAMILIA SIMPSONS, FAMILIA STICH, FAMILIA AVENGERS, FAMILIA IROMAN, FAMILIA CAPITAN AMERICA</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA</t>
+          <t>DISPONIBLES PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/kyjp725ch0b_1784991424843.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/iorl7i3h4x_1785715610130.webp</t>
         </is>
       </c>
       <c r="P83" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>7dcbe20c-5963-40c3-8164-3fe454daac65</t>
+          <t>35feb43b-d4ee-4cd0-97a4-a6461daee102</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PANTALON PAREJA (Copia)</t>
+          <t>PIJAMA FAMILIAR NAVIDEÑAS</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>pijama-pareja</t>
+          <t>familiar</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Única</t>
-        </is>
-      </c>
+      <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="n">
-        <v>77000</v>
+        <v>3</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>57000</v>
+        <v>2</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>55000</v>
+        <v>1</v>
       </c>
       <c r="J84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -5828,17 +5824,17 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>BUGEES, VEGETA Y BULMA, PICAPIEDRAS, OSO BALENCIAGA, SIMPSOM DONA, AVENGERS, IRONAM, STICH, CAPITAN AMERICA, CAPIBARA, TOM Y JERRY, SUPERMAN</t>
+          <t>Grinch Enojado, Reno Nuevo, Santa y Mickey, Papá Noel reno, Santa Nieve, STICH, MICKEY, STICH ROJO, GRINCH ARBOLITO, STICH AZUL, MICKEY ROJO, MICKEY ARBOLITO, STICH BLANCO</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>TALLAS UNICA</t>
+          <t>DISPONIBLES EN TALLAS PARA TODA LA FAMILIA</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qxxc3xmungo_1787192967336.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/uo66j97t3qc_1789404070898.webp</t>
         </is>
       </c>
       <c r="P84" s="2" t="n">
@@ -5848,13 +5844,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>89c96356-7731-47ac-bb8d-a4c4806c97c9</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr"/>
+          <t>237051ec-4251-4654-9e91-8b031dd0ac56</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>HOM-002</t>
+        </is>
+      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>PIJAMA PAREJA CORTA</t>
+          <t>PANTALON CAMISERA PAREJA</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5869,13 +5869,13 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>66000</v>
+        <v>95000</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>46000</v>
+        <v>75000</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>44000</v>
+        <v>73000</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0</v>
@@ -5890,38 +5890,38 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>SCOBBY DOOD, DONALD y DEISY, BATMAN, OSO BALENCIAGA</t>
+          <t>BATMAN, STAR WARS</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>TALLAS UNICAS SEDEN HASTA UNA TALLA L</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L COMPRENDE LA PAREJA</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/k8f75qd94x_1791060978764.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/kyjp725ch0b_1784991424843.jpg</t>
         </is>
       </c>
       <c r="P85" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1badab66-f476-403e-b23d-0eee029edbb5</t>
+          <t>7dcbe20c-5963-40c3-8164-3fe454daac65</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>JUANITA BOLERO SUBLIMADA</t>
+          <t>PIJAMA PANTALON PAREJA (Copia)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>shortiras</t>
+          <t>pijama-pareja</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -5931,13 +5931,13 @@
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>30000</v>
+        <v>77000</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>20000</v>
+        <v>57000</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>190000</v>
+        <v>55000</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0</v>
@@ -5952,38 +5952,38 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>AVOCADO FUCSIA, GARFIELD, DEISY, OSO PANDA</t>
+          <t>BUGEES, VEGETA Y BULMA, PICAPIEDRAS, OSO BALENCIAGA, SIMPSOM DONA, AVENGERS, IRONAM, STICH, CAPITAN AMERICA, CAPIBARA, TOM Y JERRY, SUPERMAN</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>TALLAS UNICA</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/so5z20eowjo_1791398900377.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qxxc3xmungo_1787192967336.webp</t>
         </is>
       </c>
       <c r="P86" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>54e67993-b96c-4d86-93f3-bcfcda1a7d6c</t>
+          <t>89c96356-7731-47ac-bb8d-a4c4806c97c9</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>SHORT LOLITA NAVIDAD</t>
+          <t>PIJAMA PAREJA CORTA</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>shortiras</t>
+          <t>pijama-pareja</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -5993,13 +5993,13 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>28000</v>
+        <v>66000</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>18000</v>
+        <v>46000</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>17000</v>
+        <v>44000</v>
       </c>
       <c r="J87" s="3" t="n">
         <v>0</v>
@@ -6014,33 +6014,33 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>CAMPANAS</t>
+          <t>SCOBBY DOOD, DONALD y DEISY, BATMAN, OSO BALENCIAGA</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
+          <t>TALLAS UNICAS SEDEN HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ogs30ui080p_1791926800097.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/k8f75qd94x_1791060978764.webp</t>
         </is>
       </c>
       <c r="P87" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>f5e1c702-f8aa-4aa1-a440-26853e562d01</t>
+          <t>1badab66-f476-403e-b23d-0eee029edbb5</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>JUANITA BOLERO UNICOLOR</t>
+          <t>JUANITA BOLERO SUBLIMADA</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>16000</v>
+        <v>190000</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>0</v>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
+          <t>AVOCADO FUCSIA, GARFIELD, DEISY, OSO PANDA</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6086,27 +6086,23 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/so5z20eowjo_1791398900377.webp</t>
         </is>
       </c>
       <c r="P88" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>STU-001</t>
-        </is>
-      </c>
+          <t>54e67993-b96c-4d86-93f3-bcfcda1a7d6c</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA</t>
+          <t>SHORT LOLITA NAVIDAD</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -6121,13 +6117,13 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="J89" s="3" t="n">
         <v>0</v>
@@ -6142,37 +6138,33 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
+          <t>CAMPANAS</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ogs30ui080p_1791926800097.webp</t>
         </is>
       </c>
       <c r="P89" s="2" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>SHD-001</t>
-        </is>
-      </c>
+          <t>f5e1c702-f8aa-4aa1-a440-26853e562d01</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA MUNDIALISTA</t>
+          <t>JUANITA BOLERO UNICOLOR</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -6183,23 +6175,23 @@
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>25000</v>
+        <v>27000</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="J90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -6208,64 +6200,64 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
+          <t>TALLA UNICA</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
         </is>
       </c>
       <c r="P90" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>76053564-24d2-4662-9825-a044ec66f57a</t>
+          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SHD-004</t>
+          <t>STU-001</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA PLUS</t>
+          <t>SHORT TIRA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>shorts</t>
+          <t>shortiras</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>33000</v>
+        <v>25000</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>23000</v>
+        <v>15000</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -6274,60 +6266,64 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>OSO DORMILON, KOALA, JIRAFFA, PANTERA ROSA</t>
+          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA PLUS SEDEN HASTA UNA TALLA XL</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxh01qefg3v_1784913347039.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>1dfacdb0-1d31-4c49-9a3e-ae522295b8e1</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr"/>
+          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SHD-001</t>
+        </is>
+      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>TRIO PANDA NAVIDAD</t>
+          <t>SHORT TIRA MUNDIALISTA</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>shorts</t>
+          <t>shortiras</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Única, Plus, Oversize</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>19000</v>
+        <v>14000</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -6336,33 +6332,37 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>SANAT TRINEO, SANTA CARICATURA, SANTA TRINEO</t>
+          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
+          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/9yveawjb88_1791927248517.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2cd0b6cd-a7bc-4009-ab40-34050bc02a02</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr"/>
+          <t>76053564-24d2-4662-9825-a044ec66f57a</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SHD-004</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>SHORT COQUETA TANGA NAVIDAD</t>
+          <t>SHORT CAMISA PLUS</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -6371,21 +6371,25 @@
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Plus</t>
+        </is>
+      </c>
       <c r="G93" s="3" t="n">
-        <v>27000</v>
+        <v>33000</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="J93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
@@ -6394,37 +6398,33 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>MICKEY, GRINCH, STICH ROJO</t>
+          <t>OSO DORMILON, KOALA, JIRAFFA, PANTERA ROSA</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA</t>
+          <t>SHORT CAMISA PLUS SEDEN HASTA UNA TALLA XL</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vxa9pwoeth9_1791927134958.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/cxh01qefg3v_1784913347039.jpg</t>
         </is>
       </c>
       <c r="P93" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>3bcb126b-7745-401c-b93d-acfd68a0fe7e</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>SCD1250</t>
-        </is>
-      </c>
+          <t>1dfacdb0-1d31-4c49-9a3e-ae522295b8e1</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>SHORT CAMISA</t>
+          <t>TRIO PANDA NAVIDAD</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -6439,46 +6439,170 @@
         </is>
       </c>
       <c r="G94" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>SANAT TRINEO, SANTA CARICATURA, SANTA TRINEO</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>TALLA UNICA COMPRENDE 3 PIEZAS</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/9yveawjb88_1791927248517.webp</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2cd0b6cd-a7bc-4009-ab40-34050bc02a02</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>SHORT COQUETA TANGA NAVIDAD</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>shorts</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="3" t="n">
         <v>27000</v>
       </c>
-      <c r="H94" s="3" t="n">
+      <c r="H95" s="3" t="n">
         <v>17000</v>
       </c>
-      <c r="I94" s="3" t="n">
+      <c r="I95" s="3" t="n">
         <v>16000</v>
       </c>
-      <c r="J94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="2" t="n">
+      <c r="J95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>MICKEY, GRINCH, STICH ROJO</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>TALLA UNICA</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vxa9pwoeth9_1791927134958.webp</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>3bcb126b-7745-401c-b93d-acfd68a0fe7e</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SCD1250</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>SHORT CAMISA</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>shorts</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Única</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>17000</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>OSO LILA, POLLITO, VAQUITA, GATICO FLOR, HELLO KITTY, CERDITO</t>
         </is>
       </c>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="N96" s="2" t="inlineStr">
         <is>
           <t>TALLA UNICA SEDE HASTA UNA TALLA L.</t>
         </is>
       </c>
-      <c r="O94" s="2" t="inlineStr">
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/ujg84y11p3n_1784924351434.jpg</t>
         </is>
       </c>
-      <c r="P94" s="2" t="n">
+      <c r="P96" s="2" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P94"/>
+  <autoFilter ref="A1:P96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6524,7 +6648,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
@@ -6547,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 12:34</t>
+          <t>2026-10-16 18:28</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 18:28</t>
+          <t>2026-10-17 00:33</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 00:33</t>
+          <t>2026-10-17 06:29</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 06:29</t>
+          <t>2026-10-17 12:27</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 12:27</t>
+          <t>2026-10-17 18:24</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-17 18:24</t>
+          <t>2026-10-18 00:33</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 00:33</t>
+          <t>2026-10-18 06:29</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 06:29</t>
+          <t>2026-10-18 12:27</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 12:27</t>
+          <t>2026-10-18 18:24</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-18 18:24</t>
+          <t>2026-10-19 00:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 00:34</t>
+          <t>2026-10-19 06:39</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 06:39</t>
+          <t>2026-10-19 12:37</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 12:37</t>
+          <t>2026-10-19 18:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 18:30</t>
+          <t>2026-10-20 00:36</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:36</t>
+          <t>2026-10-20 07:00</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 07:00</t>
+          <t>2026-10-20 12:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 12:34</t>
+          <t>2026-10-20 18:31</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 18:31</t>
+          <t>2026-10-21 00:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 00:34</t>
+          <t>2026-10-21 06:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 06:35</t>
+          <t>2026-10-21 01:57</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 01:57</t>
+          <t>2026-10-21 02:48</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 02:48</t>
+          <t>2026-10-21 03:31</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 03:31</t>
+          <t>2026-10-21 04:22</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 04:22</t>
+          <t>2026-10-21 12:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 12:35</t>
+          <t>2026-10-21 08:02</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Catálogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo'!$A$1:$P$96</definedName>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 08:02</t>
+          <t>2026-10-21 18:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21 18:30</t>
+          <t>2026-10-22 00:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 00:35</t>
+          <t>2026-10-22 06:35</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 06:35</t>
+          <t>2026-10-22 12:36</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 12:36</t>
+          <t>2026-10-22 18:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22 18:30</t>
+          <t>2026-10-23 00:37</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 00:37</t>
+          <t>2026-10-23 06:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 06:34</t>
+          <t>2026-10-23 12:31</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 12:31</t>
+          <t>2026-10-23 18:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -2120,7 +2120,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>AZUL, BEIZ, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO, ROJO</t>
+          <t>AZUL, LILA, NEGRO, ROSADO, BLANCO HUESO, BLANCO</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA MORADA, AVOCADO FUCSIA, STICH MORADO, KOALA, OSO LOTSO, MINNIE, CERDITO FUCSIA, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
+          <t>STICH MORADO, KOALA, OSO LOTSO, MINNIE, CAPIBARA CAFE, VAQUITA NEGRA, MICKEY NEGRO, AVOCADO, BEARS</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -2766,11 +2766,11 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/qqwsrxvr1ic_1789406839500.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/dvn5kd4fejc_1789406841873.webp</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SANTA, SANTA CARICATURAS, SANTA TRINEO</t>
+          <t>SANTA, SANTA TRINEO</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO, PIOLIN</t>
+          <t>VAQUITA ROSA, PANTERA ROSA, SNOOPY FLOR, VAQUITA MOÑO, WINE POOH, ELMO, DONALD, GARFIELD, ELEFANTE, PUCCA, GATICA, OSA MOÑO, OSO, CUTR PUPPY, GATICA MOÑO, CUTE SWAN, CERDITO</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, HELLO KITTY, PATO DONALD</t>
+          <t>KITTY, CAPIBARA, LABUBU, Oso lottso, PANTERA ROSA, SNOOPY, CAPIBARA CAFE, JIRAFA TIERNA, PATO DONALD</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="P55" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE, HELLO KITTY</t>
+          <t>CAPIBARA, VAQUITA MOO, DEISY, MAFALDA MORADO, OSO CARIÑOSO, MINNIE</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>OJOS, MINNIE, HELLO KITTY, OSO PANDA, STICH</t>
+          <t>OJOS, MINNIE, OSO PANDA, STICH</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1003145115, RULERGS, OSO ANTIFAZ, COFFE, PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/q027f72zlv8_1784914996896.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
+          <t>POCHACO, CAPIBARA NARANJA, CINAMORROL, BURBUJA, 1002416596</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -5470,11 +5470,11 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/e0wxiek6bya_1784951657522.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/1pwd5aw4xvn_1784951658664.jpg</t>
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>HELLO KITTY, OSO LOTSO, MICKEY, PIOLIN, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, AVOCADO FUCSIA, BOB BONNY, STICH, CUTE, OSO PANDA, MAFALDA, PIOLIN AMARILLO, OVEJA NUVE, MY MELODDY, OSA</t>
+          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6276,11 +6276,11 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/wq6vkaejj3f_1784922917937.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23 18:30</t>
+          <t>2026-10-24 00:40</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>1</v>
@@ -5749,7 +5749,7 @@
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
@@ -5803,10 +5803,10 @@
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="3" t="n">
-        <v>3</v>
+        <v>36000</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2</v>
+        <v>26000</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>1</v>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 00:40</t>
+          <t>2026-10-24 06:29</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 06:29</t>
+          <t>2026-10-24 12:28</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 12:28</t>
+          <t>2026-10-24 18:25</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24 18:25</t>
+          <t>2026-10-25 00:30</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 00:30</t>
+          <t>2026-10-25 06:31</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 06:31</t>
+          <t>2026-10-25 12:28</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 12:28</t>
+          <t>2026-10-25 18:25</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 18:25</t>
+          <t>2026-10-26 00:43</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 00:43</t>
+          <t>2026-10-26 06:40</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 06:40</t>
+          <t>2026-10-26 14:42</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>AMARILLO, SALMON, ROSA, ROSADO, AZUL, LILA</t>
+          <t>AMARILLO, SALMON, AZUL, LILA</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>TOTTO, WINNE POOH, WINNE POOH LILA</t>
+          <t>TOTTO, WINNE POOH</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="P74" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>MINNIE, DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
+          <t>DONAL Y DEISY, 1002612353, LABUBU CAFE, VAQUITA ESPACIAL, MICKEY, MINNIE AZUL, HELLO KITTY</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -5536,11 +5536,11 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/njirlp0s9_1784991741310.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/2i5ai5chp2u_1784991743787.jpg</t>
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>FUCSIA, ROJA, BEIZ, NEGRO, ROSA, BLANCO HUESO, AZUL TURQUI</t>
+          <t>ROJA, NEGRO, BLANCO HUESO</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -6210,11 +6210,11 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/w20s9ddim4r_1791399518651.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/lm6eiuewqld_1791399520169.webp</t>
         </is>
       </c>
       <c r="P90" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 14:42</t>
+          <t>2026-10-26 18:40</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 18:40</t>
+          <t>2026-10-27 00:34</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:34</t>
+          <t>2026-10-27 06:37</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 06:37</t>
+          <t>2026-10-27 12:39</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 12:39</t>
+          <t>2026-10-27 18:40</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 18:40</t>
+          <t>2026-10-28 00:44</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 00:44</t>
+          <t>2026-10-28 06:43</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6671,7 +6671,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 06:43</t>
+          <t>2026-10-28 12:44</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1004165238, 1004165237, 1004165236, 1004165235, 1004165234, 1004165233, 1004165232, 1004165231, 1004165230, 1004165229, 1004165228, 1004165227, 1004165226, 1004165225, 1004165224, 1004165218</t>
+          <t>1004165237, 1004165234, 1004165233, 1004165232, 1004165231, 1004165230, 1004165227, 1004165226, 1004165224, 1004165218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/j7a765w02fc_1792168079354.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/g3gm0hniit5_1792168080708.webp</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3249,7 +3249,11 @@
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2/4, 6/8, 10/12, 14/16</t>
+        </is>
+      </c>
       <c r="G44" s="3" t="n">
         <v>25000</v>
       </c>
@@ -3270,7 +3274,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>CINAMORROL, CERDITO, AVOCADO, STICH, BLANCA NIEVES, BOB ESPONJA, CAPIBARA, GUERRERAS KPOP, GATA MARIE, LILO Y STICH, PERRO MORADO, OSITA GLOBOS</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>TALLAS 2/4-6/8-10/12-14/16 TALLAJE NORMAL</t>
@@ -6660,7 +6668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -6671,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 12:44</t>
+          <t>2026-10-28 18:41</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28 18:41</t>
+          <t>2026-10-29 00:44</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:44</t>
+          <t>2026-10-29 06:46</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 06:46</t>
+          <t>2026-10-29 12:46</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 12:46</t>
+          <t>2026-10-29 18:44</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 18:44</t>
+          <t>2026-10-30 00:45</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -4774,17 +4774,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
+          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SET104</t>
+          <t>STP-002</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>SHORT TIRA PLUS</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
@@ -4820,37 +4820,37 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
+          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>SHORT ESQUELETO TALLA UNICA</t>
+          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>f76a5f9c-6d1c-470d-9ad3-58f6c5a4fc8a</t>
+          <t>23141b4f-2a7f-46ad-af38-1c09e3487a0a</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>STP-002</t>
+          <t>SET104</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
@@ -4886,21 +4886,21 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>PRINCESA MARIO, DINO BEAR, GATO FRESA</t>
+          <t>STICH ROSADO, STICH MORADO, STICH AZUL, STICH BLANCO</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA PLUS SEDEN HASTA UNA XL</t>
+          <t>SHORT ESQUELETO TALLA UNICA</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/aeirxq4xmf_1789406213691.webp</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/8nrg5mb3ft6_1784908267309.jpg</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -6228,17 +6228,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
+          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>STU-001</t>
+          <t>SHD-001</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA</t>
+          <t>SHORT TIRA MUNDIALISTA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -6249,7 +6249,7 @@
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Única</t>
+          <t>Única, Plus, Oversize</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
@@ -6265,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
@@ -6274,37 +6274,37 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
+          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
+          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>cc4b475f-d7d8-47bd-a3d6-73439ec7046b</t>
+          <t>ceed2bf1-60e4-41c8-a23f-372380343eea</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SHD-001</t>
+          <t>STU-001</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA MUNDIALISTA</t>
+          <t>SHORT TIRA</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Única, Plus, Oversize</t>
+          <t>Única</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
@@ -6340,21 +6340,21 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>SHORT TIRA AL ESTILO MUNDIAL</t>
+          <t>TALLA UNICA SEDE HASTA UNA TALLA L</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/vt26asit3lo_1784684759726.jpg</t>
+          <t>https://dowbsbxvxjzjjhyqmyfr.supabase.co/storage/v1/object/public/archivos/jxcws9687y_1784922919118.jpg</t>
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:45</t>
+          <t>2026-10-30 06:47</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 06:47</t>
+          <t>2026-10-30 12:46</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 12:46</t>
+          <t>2026-10-30 18:40</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6274,7 +6274,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>BRAZIL 2, BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
+          <t>BRAZIL, COLOMBIA 2, COLOMBIA, FRANCIA</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>OSO LOTSO, MICKEY, HELLO KITTY, TIGERS, PINGUINOS, AVOCADO, CERDITO, CAPIBARA, BAMBI, PALETA LILA, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, STICH, OSO PANDA, MAFALDA, OVEJA NUVE, MY MELODDY</t>
+          <t>OSO LOTSO, MICKEY, TIGERS, AVOCADO, CERDITO, BOB ESPONJA, CINAMORROL, MINNI FLOR, ELEFANTE, MAFALDA, OVEJA NUVE, MY MELODDY</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 18:40</t>
+          <t>2026-10-31 00:51</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 00:51</t>
+          <t>2026-10-31 06:44</t>
         </is>
       </c>
     </row>

--- a/Sublimados_Majestic_Catalogo.xlsx
+++ b/Sublimados_Majestic_Catalogo.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 06:44</t>
+          <t>2026-10-31 12:41</t>
         </is>
       </c>
     </row>
